--- a/data/stx_xlsx/DIOS.ST.xlsx
+++ b/data/stx_xlsx/DIOS.ST.xlsx
@@ -12,14 +12,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="TNKSDmGMSVWEWG19skL/E9zEkwoprTvFdX+o9fEtGeo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="I6zA85jefNTiYKg+EFzFNXiu2U7A3L4dzLS9Ezm/g7M="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="347">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -10416,10 +10416,18 @@
       <c r="A55" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
+      <c r="B55" s="16">
+        <v>3105.45</v>
+      </c>
+      <c r="C55" s="16">
+        <v>3257.01</v>
+      </c>
+      <c r="D55" s="16">
+        <v>6617.46</v>
+      </c>
+      <c r="E55" s="16">
+        <v>5156.25</v>
+      </c>
       <c r="F55" s="16">
         <v>5533.9</v>
       </c>
@@ -10472,137 +10480,137 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="16">
-        <v>3105.45</v>
-      </c>
-      <c r="C56" s="16">
-        <v>3257.01</v>
-      </c>
-      <c r="D56" s="16">
-        <v>6617.46</v>
+        <v>156.37</v>
+      </c>
+      <c r="C56" s="17">
+        <v>21.59</v>
+      </c>
+      <c r="D56" s="17">
+        <v>92.62</v>
       </c>
       <c r="E56" s="16">
-        <v>5156.25</v>
-      </c>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
+        <v>136.48</v>
+      </c>
+      <c r="F56" s="17">
+        <v>23.38</v>
+      </c>
+      <c r="G56" s="17">
+        <v>96.07</v>
+      </c>
+      <c r="H56" s="16">
+        <v>132.21</v>
+      </c>
+      <c r="I56" s="16">
+        <v>123.93</v>
+      </c>
+      <c r="J56" s="17">
+        <v>64.04</v>
+      </c>
+      <c r="K56" s="16">
+        <v>110.0</v>
+      </c>
       <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="15"/>
-      <c r="S56" s="15"/>
-      <c r="T56" s="15"/>
-      <c r="U56" s="15"/>
-      <c r="V56" s="15"/>
+      <c r="M56" s="16">
+        <v>190.74</v>
+      </c>
+      <c r="N56" s="16">
+        <v>107.44</v>
+      </c>
+      <c r="O56" s="16">
+        <v>190.48</v>
+      </c>
+      <c r="P56" s="16">
+        <v>168.24</v>
+      </c>
+      <c r="Q56" s="17">
+        <v>52.78</v>
+      </c>
+      <c r="R56" s="17">
+        <v>62.58</v>
+      </c>
+      <c r="S56" s="16">
+        <v>108.83</v>
+      </c>
+      <c r="T56" s="17">
+        <v>4.74</v>
+      </c>
+      <c r="U56" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="V56" s="17">
+        <v>59.95</v>
+      </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B57" s="16">
-        <v>156.37</v>
-      </c>
-      <c r="C57" s="17">
-        <v>21.59</v>
-      </c>
-      <c r="D57" s="17">
-        <v>92.62</v>
-      </c>
-      <c r="E57" s="16">
-        <v>136.48</v>
-      </c>
-      <c r="F57" s="17">
-        <v>23.38</v>
+        <v>198</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="E57" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="F57" s="15">
+        <v>0.0</v>
       </c>
       <c r="G57" s="17">
-        <v>96.07</v>
+        <v>65.78</v>
       </c>
       <c r="H57" s="16">
-        <v>132.21</v>
+        <v>193.16</v>
       </c>
       <c r="I57" s="16">
-        <v>123.93</v>
-      </c>
-      <c r="J57" s="17">
-        <v>64.04</v>
-      </c>
-      <c r="K57" s="16">
-        <v>110.0</v>
-      </c>
-      <c r="L57" s="15"/>
-      <c r="M57" s="16">
-        <v>190.74</v>
-      </c>
-      <c r="N57" s="16">
-        <v>107.44</v>
-      </c>
-      <c r="O57" s="16">
-        <v>190.48</v>
-      </c>
-      <c r="P57" s="16">
-        <v>168.24</v>
-      </c>
-      <c r="Q57" s="17">
-        <v>52.78</v>
-      </c>
-      <c r="R57" s="17">
-        <v>62.58</v>
-      </c>
-      <c r="S57" s="16">
-        <v>108.83</v>
-      </c>
-      <c r="T57" s="17">
-        <v>4.74</v>
-      </c>
-      <c r="U57" s="17">
-        <v>0.65</v>
-      </c>
-      <c r="V57" s="17">
-        <v>59.95</v>
-      </c>
+        <v>193.22</v>
+      </c>
+      <c r="J57" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K57" s="17">
+        <v>14.22</v>
+      </c>
+      <c r="L57" s="16">
+        <v>237.57</v>
+      </c>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="15"/>
+      <c r="T57" s="15"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="15"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="E58" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F58" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="G58" s="17">
-        <v>65.78</v>
-      </c>
-      <c r="H58" s="16">
-        <v>193.16</v>
-      </c>
-      <c r="I58" s="16">
-        <v>193.22</v>
-      </c>
-      <c r="J58" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K58" s="17">
-        <v>14.22</v>
-      </c>
-      <c r="L58" s="16">
-        <v>237.57</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B58" s="17">
+        <v>12.03</v>
+      </c>
+      <c r="C58" s="17">
+        <v>8.22</v>
+      </c>
+      <c r="D58" s="17">
+        <v>9.06</v>
+      </c>
+      <c r="E58" s="17">
+        <v>6.59</v>
+      </c>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
       <c r="O58" s="15"/>
@@ -10616,27 +10624,41 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="17">
-        <v>12.03</v>
+        <v>71.08</v>
       </c>
       <c r="C59" s="17">
-        <v>8.22</v>
-      </c>
-      <c r="D59" s="17">
-        <v>9.06</v>
-      </c>
-      <c r="E59" s="17">
-        <v>6.59</v>
-      </c>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
+        <v>37.01</v>
+      </c>
+      <c r="D59" s="16">
+        <v>383.58</v>
+      </c>
+      <c r="E59" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="F59" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="G59" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="H59" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I59" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J59" s="17">
+        <v>16.01</v>
+      </c>
+      <c r="K59" s="17">
+        <v>40.78</v>
+      </c>
+      <c r="L59" s="16">
+        <v>140.24</v>
+      </c>
       <c r="M59" s="15"/>
       <c r="N59" s="15"/>
       <c r="O59" s="15"/>
@@ -10650,319 +10672,319 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B60" s="17">
-        <v>71.08</v>
+        <v>62.33</v>
       </c>
       <c r="C60" s="17">
-        <v>37.01</v>
+        <v>58.6</v>
       </c>
       <c r="D60" s="16">
-        <v>383.58</v>
-      </c>
-      <c r="E60" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F60" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="G60" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="H60" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I60" s="15">
-        <v>0.0</v>
+        <v>143.97</v>
+      </c>
+      <c r="E60" s="16">
+        <v>149.66</v>
+      </c>
+      <c r="F60" s="17">
+        <v>78.92</v>
+      </c>
+      <c r="G60" s="16">
+        <v>100.24</v>
+      </c>
+      <c r="H60" s="16">
+        <v>110.64</v>
+      </c>
+      <c r="I60" s="17">
+        <v>53.67</v>
       </c>
       <c r="J60" s="17">
-        <v>16.01</v>
+        <v>35.02</v>
       </c>
       <c r="K60" s="17">
-        <v>40.78</v>
-      </c>
-      <c r="L60" s="16">
-        <v>140.24</v>
-      </c>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
-      <c r="P60" s="15"/>
-      <c r="Q60" s="15"/>
-      <c r="R60" s="15"/>
-      <c r="S60" s="15"/>
-      <c r="T60" s="15"/>
-      <c r="U60" s="15"/>
+        <v>53.11</v>
+      </c>
+      <c r="L60" s="17">
+        <v>63.84</v>
+      </c>
+      <c r="M60" s="17">
+        <v>54.63</v>
+      </c>
+      <c r="N60" s="17">
+        <v>83.88</v>
+      </c>
+      <c r="O60" s="17">
+        <v>67.72</v>
+      </c>
+      <c r="P60" s="17">
+        <v>84.69</v>
+      </c>
+      <c r="Q60" s="17">
+        <v>31.29</v>
+      </c>
+      <c r="R60" s="17">
+        <v>26.89</v>
+      </c>
+      <c r="S60" s="17">
+        <v>23.57</v>
+      </c>
+      <c r="T60" s="17">
+        <v>67.3</v>
+      </c>
+      <c r="U60" s="17">
+        <v>23.65</v>
+      </c>
       <c r="V60" s="15"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="B61" s="17">
-        <v>62.33</v>
-      </c>
-      <c r="C61" s="17">
-        <v>58.6</v>
+        <v>202</v>
+      </c>
+      <c r="B61" s="16">
+        <v>821.19</v>
+      </c>
+      <c r="C61" s="16">
+        <v>757.71</v>
       </c>
       <c r="D61" s="16">
-        <v>143.97</v>
+        <v>665.47</v>
       </c>
       <c r="E61" s="16">
-        <v>149.66</v>
-      </c>
-      <c r="F61" s="17">
-        <v>78.92</v>
+        <v>563.82</v>
+      </c>
+      <c r="F61" s="16">
+        <v>499.8</v>
       </c>
       <c r="G61" s="16">
-        <v>100.24</v>
+        <v>511.66</v>
       </c>
       <c r="H61" s="16">
-        <v>110.64</v>
-      </c>
-      <c r="I61" s="17">
-        <v>53.67</v>
-      </c>
-      <c r="J61" s="17">
-        <v>35.02</v>
-      </c>
-      <c r="K61" s="17">
-        <v>53.11</v>
-      </c>
-      <c r="L61" s="17">
-        <v>63.84</v>
-      </c>
-      <c r="M61" s="17">
-        <v>54.63</v>
-      </c>
-      <c r="N61" s="17">
-        <v>83.88</v>
-      </c>
-      <c r="O61" s="17">
-        <v>67.72</v>
-      </c>
-      <c r="P61" s="17">
-        <v>84.69</v>
-      </c>
-      <c r="Q61" s="17">
-        <v>31.29</v>
-      </c>
-      <c r="R61" s="17">
-        <v>26.89</v>
-      </c>
-      <c r="S61" s="17">
-        <v>23.57</v>
-      </c>
-      <c r="T61" s="17">
-        <v>67.3</v>
-      </c>
-      <c r="U61" s="17">
-        <v>23.65</v>
-      </c>
+        <v>475.4</v>
+      </c>
+      <c r="I61" s="16">
+        <v>367.9</v>
+      </c>
+      <c r="J61" s="16">
+        <v>396.26</v>
+      </c>
+      <c r="K61" s="16">
+        <v>328.12</v>
+      </c>
+      <c r="L61" s="16">
+        <v>345.37</v>
+      </c>
+      <c r="M61" s="16">
+        <v>291.38</v>
+      </c>
+      <c r="N61" s="16">
+        <v>272.37</v>
+      </c>
+      <c r="O61" s="15"/>
+      <c r="P61" s="15"/>
+      <c r="Q61" s="15"/>
+      <c r="R61" s="15"/>
+      <c r="S61" s="15"/>
+      <c r="T61" s="15"/>
+      <c r="U61" s="15"/>
       <c r="V61" s="15"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B62" s="16">
-        <v>821.19</v>
+        <v>512.84</v>
       </c>
       <c r="C62" s="16">
-        <v>757.71</v>
+        <v>459.56</v>
       </c>
       <c r="D62" s="16">
-        <v>665.47</v>
+        <v>442.98</v>
       </c>
       <c r="E62" s="16">
-        <v>563.82</v>
+        <v>381.21</v>
       </c>
       <c r="F62" s="16">
-        <v>499.8</v>
+        <v>322.49</v>
       </c>
       <c r="G62" s="16">
-        <v>511.66</v>
+        <v>334.14</v>
       </c>
       <c r="H62" s="16">
-        <v>475.4</v>
+        <v>319.74</v>
       </c>
       <c r="I62" s="16">
-        <v>367.9</v>
+        <v>279.1</v>
       </c>
       <c r="J62" s="16">
-        <v>396.26</v>
+        <v>302.2</v>
       </c>
       <c r="K62" s="16">
-        <v>328.12</v>
+        <v>227.6</v>
       </c>
       <c r="L62" s="16">
-        <v>345.37</v>
+        <v>230.24</v>
       </c>
       <c r="M62" s="16">
-        <v>291.38</v>
+        <v>204.16</v>
       </c>
       <c r="N62" s="16">
-        <v>272.37</v>
-      </c>
-      <c r="O62" s="15"/>
-      <c r="P62" s="15"/>
-      <c r="Q62" s="15"/>
-      <c r="R62" s="15"/>
-      <c r="S62" s="15"/>
+        <v>179.07</v>
+      </c>
+      <c r="O62" s="16">
+        <v>185.83</v>
+      </c>
+      <c r="P62" s="16">
+        <v>196.86</v>
+      </c>
+      <c r="Q62" s="17">
+        <v>43.37</v>
+      </c>
+      <c r="R62" s="17">
+        <v>33.39</v>
+      </c>
+      <c r="S62" s="17">
+        <v>38.67</v>
+      </c>
       <c r="T62" s="15"/>
       <c r="U62" s="15"/>
       <c r="V62" s="15"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="B63" s="16">
-        <v>512.84</v>
-      </c>
-      <c r="C63" s="16">
-        <v>459.56</v>
-      </c>
-      <c r="D63" s="16">
-        <v>442.98</v>
-      </c>
-      <c r="E63" s="16">
-        <v>381.21</v>
-      </c>
-      <c r="F63" s="16">
-        <v>322.49</v>
-      </c>
-      <c r="G63" s="16">
-        <v>334.14</v>
-      </c>
-      <c r="H63" s="16">
-        <v>319.74</v>
-      </c>
-      <c r="I63" s="16">
-        <v>279.1</v>
-      </c>
-      <c r="J63" s="16">
-        <v>302.2</v>
-      </c>
-      <c r="K63" s="16">
-        <v>227.6</v>
-      </c>
-      <c r="L63" s="16">
-        <v>230.24</v>
-      </c>
-      <c r="M63" s="16">
-        <v>204.16</v>
-      </c>
-      <c r="N63" s="16">
-        <v>179.07</v>
-      </c>
-      <c r="O63" s="16">
-        <v>185.83</v>
-      </c>
-      <c r="P63" s="16">
-        <v>196.86</v>
+        <v>204</v>
+      </c>
+      <c r="B63" s="17">
+        <v>45.93</v>
+      </c>
+      <c r="C63" s="17">
+        <v>71.97</v>
+      </c>
+      <c r="D63" s="17">
+        <v>50.34</v>
+      </c>
+      <c r="E63" s="17">
+        <v>8.47</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4.87</v>
+      </c>
+      <c r="G63" s="17">
+        <v>5.22</v>
+      </c>
+      <c r="H63" s="17">
+        <v>9.38</v>
+      </c>
+      <c r="I63" s="17">
+        <v>10.73</v>
+      </c>
+      <c r="J63" s="17">
+        <v>14.01</v>
+      </c>
+      <c r="K63" s="17">
+        <v>47.42</v>
+      </c>
+      <c r="L63" s="17">
+        <v>38.72</v>
+      </c>
+      <c r="M63" s="17">
+        <v>87.22</v>
+      </c>
+      <c r="N63" s="17">
+        <v>93.3</v>
+      </c>
+      <c r="O63" s="17">
+        <v>79.53</v>
+      </c>
+      <c r="P63" s="17">
+        <v>51.88</v>
       </c>
       <c r="Q63" s="17">
-        <v>43.37</v>
+        <v>41.33</v>
       </c>
       <c r="R63" s="17">
-        <v>33.39</v>
+        <v>35.13</v>
       </c>
       <c r="S63" s="17">
-        <v>38.67</v>
-      </c>
-      <c r="T63" s="15"/>
-      <c r="U63" s="15"/>
+        <v>59.56</v>
+      </c>
+      <c r="T63" s="17">
+        <v>81.83</v>
+      </c>
+      <c r="U63" s="17">
+        <v>53.61</v>
+      </c>
       <c r="V63" s="15"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B64" s="17">
-        <v>45.93</v>
+        <v>28.43</v>
       </c>
       <c r="C64" s="17">
-        <v>71.97</v>
+        <v>23.65</v>
       </c>
       <c r="D64" s="17">
-        <v>50.34</v>
-      </c>
-      <c r="E64" s="17">
-        <v>8.47</v>
-      </c>
-      <c r="F64" s="17">
-        <v>4.87</v>
-      </c>
-      <c r="G64" s="17">
-        <v>5.22</v>
-      </c>
-      <c r="H64" s="17">
-        <v>9.38</v>
-      </c>
-      <c r="I64" s="17">
-        <v>10.73</v>
-      </c>
-      <c r="J64" s="17">
-        <v>14.01</v>
-      </c>
-      <c r="K64" s="17">
-        <v>47.42</v>
-      </c>
-      <c r="L64" s="17">
-        <v>38.72</v>
-      </c>
-      <c r="M64" s="17">
-        <v>87.22</v>
-      </c>
-      <c r="N64" s="17">
-        <v>93.3</v>
-      </c>
-      <c r="O64" s="17">
-        <v>79.53</v>
-      </c>
-      <c r="P64" s="17">
-        <v>51.88</v>
-      </c>
-      <c r="Q64" s="17">
-        <v>41.33</v>
-      </c>
-      <c r="R64" s="17">
-        <v>35.13</v>
-      </c>
-      <c r="S64" s="17">
-        <v>59.56</v>
-      </c>
-      <c r="T64" s="17">
-        <v>81.83</v>
-      </c>
-      <c r="U64" s="17">
-        <v>53.61</v>
-      </c>
+        <v>18.12</v>
+      </c>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="15"/>
+      <c r="Q64" s="15"/>
+      <c r="R64" s="15"/>
+      <c r="S64" s="15"/>
+      <c r="T64" s="15"/>
+      <c r="U64" s="15"/>
       <c r="V64" s="15"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="B65" s="17">
-        <v>28.43</v>
-      </c>
-      <c r="C65" s="17">
-        <v>23.65</v>
-      </c>
-      <c r="D65" s="17">
-        <v>18.12</v>
-      </c>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
+        <v>206</v>
+      </c>
+      <c r="B65" s="16">
+        <v>234.0</v>
+      </c>
+      <c r="C65" s="16">
+        <v>202.53</v>
+      </c>
+      <c r="D65" s="16">
+        <v>154.03</v>
+      </c>
+      <c r="E65" s="16">
+        <v>174.13</v>
+      </c>
+      <c r="F65" s="16">
+        <v>172.45</v>
+      </c>
+      <c r="G65" s="16">
+        <v>172.29</v>
+      </c>
+      <c r="H65" s="16">
+        <v>146.28</v>
+      </c>
+      <c r="I65" s="17">
+        <v>78.07</v>
+      </c>
+      <c r="J65" s="17">
+        <v>80.05</v>
+      </c>
+      <c r="K65" s="17">
+        <v>53.11</v>
+      </c>
+      <c r="L65" s="17">
+        <v>76.4</v>
+      </c>
       <c r="M65" s="15"/>
       <c r="N65" s="15"/>
       <c r="O65" s="15"/>
@@ -10976,55 +10998,39 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="B66" s="16">
-        <v>234.0</v>
-      </c>
-      <c r="C66" s="16">
-        <v>202.53</v>
-      </c>
-      <c r="D66" s="16">
-        <v>154.03</v>
-      </c>
-      <c r="E66" s="16">
-        <v>174.13</v>
-      </c>
-      <c r="F66" s="16">
-        <v>172.45</v>
-      </c>
-      <c r="G66" s="16">
-        <v>172.29</v>
-      </c>
-      <c r="H66" s="16">
-        <v>146.28</v>
-      </c>
-      <c r="I66" s="17">
-        <v>78.07</v>
-      </c>
-      <c r="J66" s="17">
-        <v>80.05</v>
-      </c>
-      <c r="K66" s="17">
-        <v>53.11</v>
-      </c>
-      <c r="L66" s="17">
-        <v>76.4</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
       <c r="M66" s="15"/>
       <c r="N66" s="15"/>
       <c r="O66" s="15"/>
       <c r="P66" s="15"/>
       <c r="Q66" s="15"/>
       <c r="R66" s="15"/>
-      <c r="S66" s="15"/>
-      <c r="T66" s="15"/>
-      <c r="U66" s="15"/>
+      <c r="S66" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="T66" s="17">
+        <v>23.66</v>
+      </c>
+      <c r="U66" s="17">
+        <v>13.44</v>
+      </c>
       <c r="V66" s="15"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -11036,29 +11042,27 @@
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
+      <c r="L67" s="17">
+        <v>58.61</v>
+      </c>
       <c r="M67" s="15"/>
       <c r="N67" s="15"/>
       <c r="O67" s="15"/>
       <c r="P67" s="15"/>
       <c r="Q67" s="15"/>
       <c r="R67" s="15"/>
-      <c r="S67" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="T67" s="17">
-        <v>23.66</v>
-      </c>
-      <c r="U67" s="17">
-        <v>13.44</v>
-      </c>
+      <c r="S67" s="15"/>
+      <c r="T67" s="15"/>
+      <c r="U67" s="15"/>
       <c r="V67" s="15"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B68" s="15"/>
+        <v>209</v>
+      </c>
+      <c r="B68" s="17">
+        <v>1.09</v>
+      </c>
       <c r="C68" s="15"/>
       <c r="D68" s="15"/>
       <c r="E68" s="15"/>
@@ -11068,13 +11072,13 @@
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="17">
-        <v>58.61</v>
-      </c>
+      <c r="L68" s="15"/>
       <c r="M68" s="15"/>
       <c r="N68" s="15"/>
       <c r="O68" s="15"/>
-      <c r="P68" s="15"/>
+      <c r="P68" s="15">
+        <v>0.0</v>
+      </c>
       <c r="Q68" s="15"/>
       <c r="R68" s="15"/>
       <c r="S68" s="15"/>
@@ -11083,289 +11087,299 @@
       <c r="V68" s="15"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B69" s="17">
-        <v>1.09</v>
-      </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
-      <c r="P69" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="15"/>
-      <c r="S69" s="15"/>
-      <c r="T69" s="15"/>
-      <c r="U69" s="15"/>
-      <c r="V69" s="15"/>
+      <c r="A69" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B69" s="19">
+        <v>4229.53</v>
+      </c>
+      <c r="C69" s="19">
+        <v>4140.14</v>
+      </c>
+      <c r="D69" s="19">
+        <v>7912.16</v>
+      </c>
+      <c r="E69" s="19">
+        <v>6012.8</v>
+      </c>
+      <c r="F69" s="19">
+        <v>6136.01</v>
+      </c>
+      <c r="G69" s="19">
+        <v>3933.5</v>
+      </c>
+      <c r="H69" s="19">
+        <v>6453.93</v>
+      </c>
+      <c r="I69" s="19">
+        <v>3098.35</v>
+      </c>
+      <c r="J69" s="19">
+        <v>2578.67</v>
+      </c>
+      <c r="K69" s="19">
+        <v>2734.0</v>
+      </c>
+      <c r="L69" s="19">
+        <v>868.65</v>
+      </c>
+      <c r="M69" s="19">
+        <v>543.47</v>
+      </c>
+      <c r="N69" s="19">
+        <v>470.29</v>
+      </c>
+      <c r="O69" s="19">
+        <v>529.73</v>
+      </c>
+      <c r="P69" s="19">
+        <v>507.91</v>
+      </c>
+      <c r="Q69" s="19">
+        <v>170.22</v>
+      </c>
+      <c r="R69" s="19">
+        <v>415.78</v>
+      </c>
+      <c r="S69" s="19">
+        <v>500.96</v>
+      </c>
+      <c r="T69" s="19">
+        <v>410.96</v>
+      </c>
+      <c r="U69" s="20">
+        <v>91.35</v>
+      </c>
+      <c r="V69" s="20">
+        <v>59.95</v>
+      </c>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B70" s="19">
-        <v>4229.53</v>
-      </c>
-      <c r="C70" s="19">
-        <v>4140.14</v>
-      </c>
-      <c r="D70" s="19">
-        <v>7912.16</v>
-      </c>
-      <c r="E70" s="19">
-        <v>6012.8</v>
-      </c>
-      <c r="F70" s="19">
-        <v>6136.01</v>
-      </c>
-      <c r="G70" s="19">
-        <v>3933.5</v>
-      </c>
-      <c r="H70" s="19">
-        <v>6453.93</v>
-      </c>
-      <c r="I70" s="19">
-        <v>3098.35</v>
-      </c>
-      <c r="J70" s="19">
-        <v>2578.67</v>
-      </c>
-      <c r="K70" s="19">
-        <v>2734.0</v>
-      </c>
-      <c r="L70" s="19">
-        <v>868.65</v>
-      </c>
-      <c r="M70" s="19">
-        <v>543.47</v>
-      </c>
-      <c r="N70" s="19">
-        <v>470.29</v>
-      </c>
-      <c r="O70" s="19">
-        <v>529.73</v>
-      </c>
-      <c r="P70" s="19">
-        <v>507.91</v>
-      </c>
-      <c r="Q70" s="19">
-        <v>170.22</v>
-      </c>
-      <c r="R70" s="19">
-        <v>415.78</v>
-      </c>
-      <c r="S70" s="19">
-        <v>500.96</v>
-      </c>
-      <c r="T70" s="19">
-        <v>410.96</v>
-      </c>
-      <c r="U70" s="20">
-        <v>91.35</v>
-      </c>
-      <c r="V70" s="20">
-        <v>59.95</v>
-      </c>
+      <c r="A70" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B70" s="15">
+        <v>15917.59</v>
+      </c>
+      <c r="C70" s="15">
+        <v>14235.01</v>
+      </c>
+      <c r="D70" s="15">
+        <v>10581.1</v>
+      </c>
+      <c r="E70" s="15">
+        <v>10147.78</v>
+      </c>
+      <c r="F70" s="16">
+        <v>8834.76</v>
+      </c>
+      <c r="G70" s="15">
+        <v>10672.78</v>
+      </c>
+      <c r="H70" s="16">
+        <v>5845.39</v>
+      </c>
+      <c r="I70" s="16">
+        <v>8471.44</v>
+      </c>
+      <c r="J70" s="16">
+        <v>9043.84</v>
+      </c>
+      <c r="K70" s="16">
+        <v>5411.11</v>
+      </c>
+      <c r="L70" s="16">
+        <v>8474.03</v>
+      </c>
+      <c r="M70" s="16">
+        <v>7345.96</v>
+      </c>
+      <c r="N70" s="16">
+        <v>7216.38</v>
+      </c>
+      <c r="O70" s="16">
+        <v>6750.13</v>
+      </c>
+      <c r="P70" s="16">
+        <v>6935.72</v>
+      </c>
+      <c r="Q70" s="16">
+        <v>3155.97</v>
+      </c>
+      <c r="R70" s="16">
+        <v>1990.82</v>
+      </c>
+      <c r="S70" s="16">
+        <v>2189.78</v>
+      </c>
+      <c r="T70" s="16">
+        <v>2042.74</v>
+      </c>
+      <c r="U70" s="16">
+        <v>1047.1</v>
+      </c>
+      <c r="V70" s="15"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="B71" s="15">
-        <v>15917.59</v>
-      </c>
-      <c r="C71" s="15">
-        <v>14235.01</v>
-      </c>
-      <c r="D71" s="15">
-        <v>10581.1</v>
-      </c>
-      <c r="E71" s="15">
-        <v>10147.78</v>
-      </c>
-      <c r="F71" s="16">
-        <v>8834.76</v>
-      </c>
-      <c r="G71" s="15">
-        <v>10672.78</v>
-      </c>
-      <c r="H71" s="16">
-        <v>5845.39</v>
-      </c>
-      <c r="I71" s="16">
-        <v>8471.44</v>
-      </c>
-      <c r="J71" s="16">
-        <v>9043.84</v>
-      </c>
-      <c r="K71" s="16">
-        <v>5411.11</v>
-      </c>
-      <c r="L71" s="16">
-        <v>8474.03</v>
-      </c>
-      <c r="M71" s="16">
-        <v>7345.96</v>
-      </c>
-      <c r="N71" s="16">
-        <v>7216.38</v>
-      </c>
-      <c r="O71" s="16">
-        <v>6750.13</v>
-      </c>
-      <c r="P71" s="16">
-        <v>6935.72</v>
-      </c>
-      <c r="Q71" s="16">
-        <v>3155.97</v>
-      </c>
-      <c r="R71" s="16">
-        <v>1990.82</v>
-      </c>
-      <c r="S71" s="16">
-        <v>2189.78</v>
-      </c>
-      <c r="T71" s="16">
-        <v>2042.74</v>
-      </c>
-      <c r="U71" s="16">
-        <v>1047.1</v>
-      </c>
-      <c r="V71" s="15"/>
+        <v>212</v>
+      </c>
+      <c r="B71" s="17">
+        <v>12.03</v>
+      </c>
+      <c r="C71" s="17">
+        <v>10.28</v>
+      </c>
+      <c r="D71" s="17">
+        <v>10.07</v>
+      </c>
+      <c r="E71" s="17">
+        <v>9.41</v>
+      </c>
+      <c r="F71" s="17">
+        <v>9.74</v>
+      </c>
+      <c r="G71" s="17">
+        <v>10.44</v>
+      </c>
+      <c r="H71" s="17">
+        <v>8.44</v>
+      </c>
+      <c r="I71" s="17">
+        <v>8.78</v>
+      </c>
+      <c r="J71" s="17">
+        <v>9.01</v>
+      </c>
+      <c r="K71" s="17">
+        <v>8.53</v>
+      </c>
+      <c r="L71" s="17">
+        <v>9.42</v>
+      </c>
+      <c r="M71" s="17">
+        <v>8.63</v>
+      </c>
+      <c r="N71" s="17">
+        <v>8.48</v>
+      </c>
+      <c r="O71" s="17">
+        <v>8.12</v>
+      </c>
+      <c r="P71" s="17">
+        <v>17.49</v>
+      </c>
+      <c r="Q71" s="17">
+        <v>12.64</v>
+      </c>
+      <c r="R71" s="17">
+        <v>9.4</v>
+      </c>
+      <c r="S71" s="17">
+        <v>4.58</v>
+      </c>
+      <c r="T71" s="17">
+        <v>4.24</v>
+      </c>
+      <c r="U71" s="17">
+        <v>3.38</v>
+      </c>
+      <c r="V71" s="17">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B72" s="17">
-        <v>12.03</v>
-      </c>
-      <c r="C72" s="17">
-        <v>10.28</v>
-      </c>
-      <c r="D72" s="17">
-        <v>10.07</v>
-      </c>
-      <c r="E72" s="17">
-        <v>9.41</v>
-      </c>
-      <c r="F72" s="17">
-        <v>9.74</v>
-      </c>
-      <c r="G72" s="17">
-        <v>10.44</v>
-      </c>
-      <c r="H72" s="17">
-        <v>8.44</v>
-      </c>
-      <c r="I72" s="17">
-        <v>8.78</v>
-      </c>
-      <c r="J72" s="17">
-        <v>9.01</v>
-      </c>
-      <c r="K72" s="17">
-        <v>8.53</v>
-      </c>
-      <c r="L72" s="17">
-        <v>9.42</v>
-      </c>
-      <c r="M72" s="17">
-        <v>8.63</v>
-      </c>
-      <c r="N72" s="17">
-        <v>8.48</v>
-      </c>
-      <c r="O72" s="17">
-        <v>8.12</v>
-      </c>
-      <c r="P72" s="17">
-        <v>17.49</v>
-      </c>
-      <c r="Q72" s="17">
-        <v>12.64</v>
-      </c>
-      <c r="R72" s="17">
-        <v>9.4</v>
-      </c>
-      <c r="S72" s="17">
-        <v>4.58</v>
-      </c>
-      <c r="T72" s="17">
-        <v>4.24</v>
-      </c>
-      <c r="U72" s="17">
-        <v>3.38</v>
-      </c>
-      <c r="V72" s="17">
-        <v>0.25</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="B72" s="16">
+        <v>2745.69</v>
+      </c>
+      <c r="C72" s="16">
+        <v>2429.39</v>
+      </c>
+      <c r="D72" s="16">
+        <v>2257.17</v>
+      </c>
+      <c r="E72" s="16">
+        <v>2243.03</v>
+      </c>
+      <c r="F72" s="16">
+        <v>2127.82</v>
+      </c>
+      <c r="G72" s="16">
+        <v>1763.66</v>
+      </c>
+      <c r="H72" s="16">
+        <v>1429.0</v>
+      </c>
+      <c r="I72" s="16">
+        <v>1320.34</v>
+      </c>
+      <c r="J72" s="16">
+        <v>1197.77</v>
+      </c>
+      <c r="K72" s="16">
+        <v>956.85</v>
+      </c>
+      <c r="L72" s="16">
+        <v>915.74</v>
+      </c>
+      <c r="M72" s="16">
+        <v>704.5</v>
+      </c>
+      <c r="N72" s="16">
+        <v>617.31</v>
+      </c>
+      <c r="O72" s="16">
+        <v>507.93</v>
+      </c>
+      <c r="P72" s="16">
+        <v>482.27</v>
+      </c>
+      <c r="Q72" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="R72" s="15"/>
+      <c r="S72" s="15"/>
+      <c r="T72" s="15"/>
+      <c r="U72" s="15"/>
+      <c r="V72" s="15"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="B73" s="16">
-        <v>2745.69</v>
-      </c>
-      <c r="C73" s="16">
-        <v>2429.39</v>
-      </c>
-      <c r="D73" s="16">
-        <v>2257.17</v>
-      </c>
-      <c r="E73" s="16">
-        <v>2243.03</v>
-      </c>
-      <c r="F73" s="16">
-        <v>2127.82</v>
-      </c>
-      <c r="G73" s="16">
-        <v>1763.66</v>
-      </c>
-      <c r="H73" s="16">
-        <v>1429.0</v>
-      </c>
-      <c r="I73" s="16">
-        <v>1320.34</v>
-      </c>
-      <c r="J73" s="16">
-        <v>1197.77</v>
-      </c>
-      <c r="K73" s="16">
-        <v>956.85</v>
-      </c>
-      <c r="L73" s="16">
-        <v>915.74</v>
-      </c>
-      <c r="M73" s="16">
-        <v>704.5</v>
-      </c>
-      <c r="N73" s="16">
-        <v>617.31</v>
-      </c>
-      <c r="O73" s="16">
-        <v>507.93</v>
-      </c>
-      <c r="P73" s="16">
-        <v>482.27</v>
-      </c>
-      <c r="Q73" s="15">
-        <v>0.0</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="B73" s="17">
+        <v>87.48</v>
+      </c>
+      <c r="C73" s="17">
+        <v>66.83</v>
+      </c>
+      <c r="D73" s="17">
+        <v>74.5</v>
+      </c>
+      <c r="E73" s="17">
+        <v>48.95</v>
+      </c>
+      <c r="F73" s="17">
+        <v>52.61</v>
+      </c>
+      <c r="G73" s="17">
+        <v>57.43</v>
+      </c>
+      <c r="H73" s="17">
+        <v>49.7</v>
+      </c>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="15"/>
+      <c r="P73" s="15"/>
+      <c r="Q73" s="15"/>
       <c r="R73" s="15"/>
       <c r="S73" s="15"/>
       <c r="T73" s="15"/>
@@ -11374,29 +11388,23 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B74" s="17">
-        <v>87.48</v>
+        <v>38.27</v>
       </c>
       <c r="C74" s="17">
-        <v>66.83</v>
+        <v>35.98</v>
       </c>
       <c r="D74" s="17">
-        <v>74.5</v>
+        <v>51.34</v>
       </c>
       <c r="E74" s="17">
-        <v>48.95</v>
-      </c>
-      <c r="F74" s="17">
-        <v>52.61</v>
-      </c>
-      <c r="G74" s="17">
-        <v>57.43</v>
-      </c>
-      <c r="H74" s="17">
-        <v>49.7</v>
-      </c>
+        <v>16.0</v>
+      </c>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
       <c r="I74" s="15"/>
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
@@ -11404,8 +11412,12 @@
       <c r="M74" s="15"/>
       <c r="N74" s="15"/>
       <c r="O74" s="15"/>
-      <c r="P74" s="15"/>
-      <c r="Q74" s="15"/>
+      <c r="P74" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="Q74" s="17">
+        <v>2.02</v>
+      </c>
       <c r="R74" s="15"/>
       <c r="S74" s="15"/>
       <c r="T74" s="15"/>
@@ -11414,20 +11426,16 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="B75" s="17">
-        <v>38.27</v>
-      </c>
-      <c r="C75" s="17">
-        <v>35.98</v>
-      </c>
-      <c r="D75" s="17">
-        <v>51.34</v>
-      </c>
-      <c r="E75" s="17">
-        <v>16.0</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B75" s="16">
+        <v>135.59</v>
+      </c>
+      <c r="C75" s="16">
+        <v>226.18</v>
+      </c>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
       <c r="F75" s="15"/>
       <c r="G75" s="15"/>
       <c r="H75" s="15"/>
@@ -11438,12 +11446,8 @@
       <c r="M75" s="15"/>
       <c r="N75" s="15"/>
       <c r="O75" s="15"/>
-      <c r="P75" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="Q75" s="17">
-        <v>2.02</v>
-      </c>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
       <c r="R75" s="15"/>
       <c r="S75" s="15"/>
       <c r="T75" s="15"/>
@@ -11452,14 +11456,10 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="B76" s="16">
-        <v>135.59</v>
-      </c>
-      <c r="C76" s="16">
-        <v>226.18</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
       <c r="F76" s="15"/>
@@ -11472,7 +11472,9 @@
       <c r="M76" s="15"/>
       <c r="N76" s="15"/>
       <c r="O76" s="15"/>
-      <c r="P76" s="15"/>
+      <c r="P76" s="15">
+        <v>0.0</v>
+      </c>
       <c r="Q76" s="15"/>
       <c r="R76" s="15"/>
       <c r="S76" s="15"/>
@@ -11481,104 +11483,108 @@
       <c r="V76" s="15"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
-      <c r="M77" s="15"/>
-      <c r="N77" s="15"/>
-      <c r="O77" s="15"/>
-      <c r="P77" s="15">
+      <c r="A77" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B77" s="22">
+        <v>18936.66</v>
+      </c>
+      <c r="C77" s="22">
+        <v>17003.67</v>
+      </c>
+      <c r="D77" s="22">
+        <v>12974.18</v>
+      </c>
+      <c r="E77" s="22">
+        <v>12465.18</v>
+      </c>
+      <c r="F77" s="22">
+        <v>11024.94</v>
+      </c>
+      <c r="G77" s="22">
+        <v>12504.3</v>
+      </c>
+      <c r="H77" s="19">
+        <v>7332.52</v>
+      </c>
+      <c r="I77" s="19">
+        <v>9800.56</v>
+      </c>
+      <c r="J77" s="22">
+        <v>10250.62</v>
+      </c>
+      <c r="K77" s="19">
+        <v>6376.49</v>
+      </c>
+      <c r="L77" s="19">
+        <v>9399.19</v>
+      </c>
+      <c r="M77" s="19">
+        <v>8059.08</v>
+      </c>
+      <c r="N77" s="19">
+        <v>7842.17</v>
+      </c>
+      <c r="O77" s="19">
+        <v>7266.18</v>
+      </c>
+      <c r="P77" s="19">
+        <v>7435.48</v>
+      </c>
+      <c r="Q77" s="19">
+        <v>3170.63</v>
+      </c>
+      <c r="R77" s="19">
+        <v>2000.22</v>
+      </c>
+      <c r="S77" s="19">
+        <v>2194.36</v>
+      </c>
+      <c r="T77" s="19">
+        <v>2046.99</v>
+      </c>
+      <c r="U77" s="19">
+        <v>1050.48</v>
+      </c>
+      <c r="V77" s="19">
+        <v>995.64</v>
+      </c>
+    </row>
+    <row r="78" ht="15.0" customHeight="1">
+      <c r="A78" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="15"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+      <c r="L78" s="15"/>
+      <c r="M78" s="15"/>
+      <c r="N78" s="15"/>
+      <c r="O78" s="15"/>
+      <c r="P78" s="26">
         <v>0.0</v>
       </c>
-      <c r="Q77" s="15"/>
-      <c r="R77" s="15"/>
-      <c r="S77" s="15"/>
-      <c r="T77" s="15"/>
-      <c r="U77" s="15"/>
-      <c r="V77" s="15"/>
-    </row>
-    <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B78" s="22">
-        <v>18936.66</v>
-      </c>
-      <c r="C78" s="22">
-        <v>17003.67</v>
-      </c>
-      <c r="D78" s="22">
-        <v>12974.18</v>
-      </c>
-      <c r="E78" s="22">
-        <v>12465.18</v>
-      </c>
-      <c r="F78" s="22">
-        <v>11024.94</v>
-      </c>
-      <c r="G78" s="22">
-        <v>12504.3</v>
-      </c>
-      <c r="H78" s="19">
-        <v>7332.52</v>
-      </c>
-      <c r="I78" s="19">
-        <v>9800.56</v>
-      </c>
-      <c r="J78" s="22">
-        <v>10250.62</v>
-      </c>
-      <c r="K78" s="19">
-        <v>6376.49</v>
-      </c>
-      <c r="L78" s="19">
-        <v>9399.19</v>
-      </c>
-      <c r="M78" s="19">
-        <v>8059.08</v>
-      </c>
-      <c r="N78" s="19">
-        <v>7842.17</v>
-      </c>
-      <c r="O78" s="19">
-        <v>7266.18</v>
-      </c>
-      <c r="P78" s="19">
-        <v>7435.48</v>
-      </c>
-      <c r="Q78" s="19">
-        <v>3170.63</v>
-      </c>
-      <c r="R78" s="19">
-        <v>2000.22</v>
-      </c>
-      <c r="S78" s="19">
-        <v>2194.36</v>
-      </c>
-      <c r="T78" s="19">
-        <v>2046.99</v>
-      </c>
-      <c r="U78" s="19">
-        <v>1050.48</v>
-      </c>
-      <c r="V78" s="19">
-        <v>995.64</v>
+      <c r="Q78" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="R78" s="15"/>
+      <c r="S78" s="15"/>
+      <c r="T78" s="15"/>
+      <c r="U78" s="15"/>
+      <c r="V78" s="16">
+        <v>995.38</v>
       </c>
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -11594,755 +11600,791 @@
       <c r="M79" s="15"/>
       <c r="N79" s="15"/>
       <c r="O79" s="15"/>
-      <c r="P79" s="26">
-        <v>0.0</v>
-      </c>
-      <c r="Q79" s="15">
+      <c r="P79" s="15"/>
+      <c r="Q79" s="26">
         <v>0.0</v>
       </c>
       <c r="R79" s="15"/>
       <c r="S79" s="15"/>
       <c r="T79" s="15"/>
       <c r="U79" s="15"/>
-      <c r="V79" s="16">
-        <v>995.38</v>
-      </c>
+      <c r="V79" s="15"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
-      <c r="M80" s="15"/>
-      <c r="N80" s="15"/>
-      <c r="O80" s="15"/>
-      <c r="P80" s="15"/>
-      <c r="Q80" s="26">
-        <v>0.0</v>
-      </c>
-      <c r="R80" s="15"/>
-      <c r="S80" s="15"/>
-      <c r="T80" s="15"/>
-      <c r="U80" s="15"/>
-      <c r="V80" s="15"/>
+      <c r="A80" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B80" s="22">
+        <v>23166.19</v>
+      </c>
+      <c r="C80" s="22">
+        <v>21143.81</v>
+      </c>
+      <c r="D80" s="22">
+        <v>20886.34</v>
+      </c>
+      <c r="E80" s="22">
+        <v>18477.98</v>
+      </c>
+      <c r="F80" s="22">
+        <v>17160.94</v>
+      </c>
+      <c r="G80" s="22">
+        <v>16437.81</v>
+      </c>
+      <c r="H80" s="22">
+        <v>13786.46</v>
+      </c>
+      <c r="I80" s="22">
+        <v>12898.91</v>
+      </c>
+      <c r="J80" s="22">
+        <v>12829.29</v>
+      </c>
+      <c r="K80" s="19">
+        <v>9110.5</v>
+      </c>
+      <c r="L80" s="22">
+        <v>10267.84</v>
+      </c>
+      <c r="M80" s="19">
+        <v>8602.55</v>
+      </c>
+      <c r="N80" s="19">
+        <v>8312.45</v>
+      </c>
+      <c r="O80" s="19">
+        <v>7795.92</v>
+      </c>
+      <c r="P80" s="19">
+        <v>7943.39</v>
+      </c>
+      <c r="Q80" s="19">
+        <v>3340.85</v>
+      </c>
+      <c r="R80" s="19">
+        <v>2416.0</v>
+      </c>
+      <c r="S80" s="19">
+        <v>2695.33</v>
+      </c>
+      <c r="T80" s="19">
+        <v>2457.95</v>
+      </c>
+      <c r="U80" s="19">
+        <v>1141.83</v>
+      </c>
+      <c r="V80" s="19">
+        <v>1055.59</v>
+      </c>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B81" s="22">
-        <v>23166.19</v>
-      </c>
-      <c r="C81" s="22">
-        <v>21143.81</v>
-      </c>
-      <c r="D81" s="22">
-        <v>20886.34</v>
-      </c>
-      <c r="E81" s="22">
-        <v>18477.98</v>
-      </c>
-      <c r="F81" s="22">
-        <v>17160.94</v>
-      </c>
-      <c r="G81" s="22">
-        <v>16437.81</v>
-      </c>
-      <c r="H81" s="22">
-        <v>13786.46</v>
-      </c>
-      <c r="I81" s="22">
-        <v>12898.91</v>
-      </c>
-      <c r="J81" s="22">
-        <v>12829.29</v>
-      </c>
-      <c r="K81" s="19">
-        <v>9110.5</v>
-      </c>
-      <c r="L81" s="22">
-        <v>10267.84</v>
-      </c>
-      <c r="M81" s="19">
-        <v>8602.55</v>
-      </c>
-      <c r="N81" s="19">
-        <v>8312.45</v>
-      </c>
-      <c r="O81" s="19">
-        <v>7795.92</v>
-      </c>
-      <c r="P81" s="19">
-        <v>7943.39</v>
-      </c>
-      <c r="Q81" s="19">
-        <v>3340.85</v>
-      </c>
-      <c r="R81" s="19">
-        <v>2416.0</v>
-      </c>
-      <c r="S81" s="19">
-        <v>2695.33</v>
-      </c>
-      <c r="T81" s="19">
-        <v>2457.95</v>
-      </c>
-      <c r="U81" s="19">
-        <v>1141.83</v>
-      </c>
-      <c r="V81" s="19">
-        <v>1055.59</v>
-      </c>
+      <c r="A81" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B81" s="16">
+        <v>310.54</v>
+      </c>
+      <c r="C81" s="16">
+        <v>291.98</v>
+      </c>
+      <c r="D81" s="16">
+        <v>285.92</v>
+      </c>
+      <c r="E81" s="16">
+        <v>267.32</v>
+      </c>
+      <c r="F81" s="16">
+        <v>276.7</v>
+      </c>
+      <c r="G81" s="16">
+        <v>280.89</v>
+      </c>
+      <c r="H81" s="16">
+        <v>252.23</v>
+      </c>
+      <c r="I81" s="16">
+        <v>262.51</v>
+      </c>
+      <c r="J81" s="16">
+        <v>269.17</v>
+      </c>
+      <c r="K81" s="16">
+        <v>141.3</v>
+      </c>
+      <c r="L81" s="16">
+        <v>155.94</v>
+      </c>
+      <c r="M81" s="16">
+        <v>142.82</v>
+      </c>
+      <c r="N81" s="16">
+        <v>140.43</v>
+      </c>
+      <c r="O81" s="16">
+        <v>127.94</v>
+      </c>
+      <c r="P81" s="16">
+        <v>129.69</v>
+      </c>
+      <c r="Q81" s="17">
+        <v>64.84</v>
+      </c>
+      <c r="R81" s="17">
+        <v>54.97</v>
+      </c>
+      <c r="S81" s="17">
+        <v>60.41</v>
+      </c>
+      <c r="T81" s="17">
+        <v>57.13</v>
+      </c>
+      <c r="U81" s="17">
+        <v>60.64</v>
+      </c>
+      <c r="V81" s="15"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B82" s="16">
-        <v>310.54</v>
+        <v>4693.16</v>
       </c>
       <c r="C82" s="16">
-        <v>291.98</v>
+        <v>4412.59</v>
       </c>
       <c r="D82" s="16">
-        <v>285.92</v>
+        <v>4321.03</v>
       </c>
       <c r="E82" s="16">
-        <v>267.32</v>
+        <v>4039.91</v>
       </c>
       <c r="F82" s="16">
-        <v>276.7</v>
+        <v>4181.6</v>
       </c>
       <c r="G82" s="16">
-        <v>280.89</v>
+        <v>3668.28</v>
       </c>
       <c r="H82" s="16">
-        <v>252.23</v>
+        <v>3294.01</v>
       </c>
       <c r="I82" s="16">
-        <v>262.51</v>
+        <v>3428.19</v>
       </c>
       <c r="J82" s="16">
-        <v>269.17</v>
+        <v>3515.27</v>
       </c>
       <c r="K82" s="16">
-        <v>141.3</v>
+        <v>1725.94</v>
       </c>
       <c r="L82" s="16">
-        <v>155.94</v>
+        <v>1904.75</v>
       </c>
       <c r="M82" s="16">
-        <v>142.82</v>
+        <v>1744.47</v>
       </c>
       <c r="N82" s="16">
-        <v>140.43</v>
+        <v>1715.27</v>
       </c>
       <c r="O82" s="16">
-        <v>127.94</v>
+        <v>1557.79</v>
       </c>
       <c r="P82" s="16">
-        <v>129.69</v>
-      </c>
-      <c r="Q82" s="17">
-        <v>64.84</v>
-      </c>
-      <c r="R82" s="17">
-        <v>54.97</v>
-      </c>
-      <c r="S82" s="17">
-        <v>60.41</v>
-      </c>
-      <c r="T82" s="17">
-        <v>57.13</v>
-      </c>
-      <c r="U82" s="17">
-        <v>60.64</v>
+        <v>1579.04</v>
+      </c>
+      <c r="Q82" s="16">
+        <v>698.93</v>
+      </c>
+      <c r="R82" s="16">
+        <v>580.67</v>
+      </c>
+      <c r="S82" s="16">
+        <v>638.16</v>
+      </c>
+      <c r="T82" s="16">
+        <v>603.55</v>
+      </c>
+      <c r="U82" s="16">
+        <v>634.13</v>
       </c>
       <c r="V82" s="15"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="B83" s="16">
-        <v>4693.16</v>
-      </c>
-      <c r="C83" s="16">
-        <v>4412.59</v>
-      </c>
-      <c r="D83" s="16">
-        <v>4321.03</v>
-      </c>
-      <c r="E83" s="16">
-        <v>4039.91</v>
-      </c>
-      <c r="F83" s="16">
-        <v>4181.6</v>
-      </c>
-      <c r="G83" s="16">
-        <v>3668.28</v>
-      </c>
-      <c r="H83" s="16">
-        <v>3294.01</v>
-      </c>
-      <c r="I83" s="16">
-        <v>3428.19</v>
-      </c>
-      <c r="J83" s="16">
-        <v>3515.27</v>
-      </c>
-      <c r="K83" s="16">
-        <v>1725.94</v>
-      </c>
-      <c r="L83" s="16">
-        <v>1904.75</v>
-      </c>
-      <c r="M83" s="16">
-        <v>1744.47</v>
-      </c>
-      <c r="N83" s="16">
-        <v>1715.27</v>
-      </c>
-      <c r="O83" s="16">
-        <v>1557.79</v>
-      </c>
-      <c r="P83" s="16">
-        <v>1579.04</v>
-      </c>
-      <c r="Q83" s="16">
-        <v>698.93</v>
-      </c>
-      <c r="R83" s="16">
-        <v>580.67</v>
-      </c>
-      <c r="S83" s="16">
-        <v>638.16</v>
-      </c>
-      <c r="T83" s="16">
-        <v>603.55</v>
-      </c>
-      <c r="U83" s="16">
-        <v>634.13</v>
+        <v>223</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
+      <c r="L83" s="15"/>
+      <c r="M83" s="15"/>
+      <c r="N83" s="15"/>
+      <c r="O83" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="P83" s="21">
+        <v>-10.28</v>
+      </c>
+      <c r="Q83" s="21">
+        <v>-14.95</v>
+      </c>
+      <c r="R83" s="21">
+        <v>-37.33</v>
+      </c>
+      <c r="S83" s="21">
+        <v>-52.52</v>
+      </c>
+      <c r="T83" s="17">
+        <v>7.68</v>
+      </c>
+      <c r="U83" s="17">
+        <v>1.32</v>
       </c>
       <c r="V83" s="15"/>
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15"/>
-      <c r="L84" s="15"/>
-      <c r="M84" s="15"/>
-      <c r="N84" s="15"/>
-      <c r="O84" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="P84" s="21">
-        <v>-10.28</v>
-      </c>
-      <c r="Q84" s="21">
-        <v>-14.95</v>
-      </c>
-      <c r="R84" s="21">
-        <v>-37.33</v>
-      </c>
-      <c r="S84" s="21">
-        <v>-52.52</v>
-      </c>
-      <c r="T84" s="17">
-        <v>7.68</v>
-      </c>
-      <c r="U84" s="17">
-        <v>1.32</v>
+        <v>224</v>
+      </c>
+      <c r="B84" s="16">
+        <v>8313.63</v>
+      </c>
+      <c r="C84" s="16">
+        <v>7283.03</v>
+      </c>
+      <c r="D84" s="16">
+        <v>6436.25</v>
+      </c>
+      <c r="E84" s="16">
+        <v>7083.96</v>
+      </c>
+      <c r="F84" s="16">
+        <v>6987.53</v>
+      </c>
+      <c r="G84" s="16">
+        <v>5543.66</v>
+      </c>
+      <c r="H84" s="16">
+        <v>4354.51</v>
+      </c>
+      <c r="I84" s="16">
+        <v>3911.25</v>
+      </c>
+      <c r="J84" s="16">
+        <v>3060.98</v>
+      </c>
+      <c r="K84" s="16">
+        <v>2182.08</v>
+      </c>
+      <c r="L84" s="16">
+        <v>1767.65</v>
+      </c>
+      <c r="M84" s="16">
+        <v>1338.07</v>
+      </c>
+      <c r="N84" s="16">
+        <v>1193.15</v>
+      </c>
+      <c r="O84" s="16">
+        <v>956.03</v>
+      </c>
+      <c r="P84" s="16">
+        <v>665.6</v>
+      </c>
+      <c r="Q84" s="16">
+        <v>568.51</v>
+      </c>
+      <c r="R84" s="16">
+        <v>335.83</v>
+      </c>
+      <c r="S84" s="16">
+        <v>314.86</v>
+      </c>
+      <c r="T84" s="16">
+        <v>483.18</v>
+      </c>
+      <c r="U84" s="16">
+        <v>411.09</v>
       </c>
       <c r="V84" s="15"/>
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B85" s="16">
-        <v>8313.63</v>
-      </c>
-      <c r="C85" s="16">
-        <v>7283.03</v>
-      </c>
-      <c r="D85" s="16">
-        <v>6436.25</v>
-      </c>
-      <c r="E85" s="16">
-        <v>7083.96</v>
-      </c>
-      <c r="F85" s="16">
-        <v>6987.53</v>
-      </c>
-      <c r="G85" s="16">
-        <v>5543.66</v>
-      </c>
-      <c r="H85" s="16">
-        <v>4354.51</v>
-      </c>
-      <c r="I85" s="16">
-        <v>3911.25</v>
-      </c>
-      <c r="J85" s="16">
-        <v>3060.98</v>
-      </c>
-      <c r="K85" s="16">
-        <v>2182.08</v>
-      </c>
-      <c r="L85" s="16">
-        <v>1767.65</v>
-      </c>
-      <c r="M85" s="16">
-        <v>1338.07</v>
-      </c>
-      <c r="N85" s="16">
-        <v>1193.15</v>
-      </c>
-      <c r="O85" s="16">
-        <v>956.03</v>
-      </c>
-      <c r="P85" s="16">
-        <v>665.6</v>
-      </c>
-      <c r="Q85" s="16">
-        <v>568.51</v>
-      </c>
-      <c r="R85" s="16">
-        <v>335.83</v>
-      </c>
-      <c r="S85" s="16">
-        <v>314.86</v>
-      </c>
-      <c r="T85" s="16">
-        <v>483.18</v>
-      </c>
-      <c r="U85" s="16">
-        <v>411.09</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="21">
+        <v>-1.03</v>
+      </c>
+      <c r="D85" s="21">
+        <v>-1.01</v>
+      </c>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="15"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="15"/>
+      <c r="L85" s="15"/>
+      <c r="M85" s="15"/>
+      <c r="N85" s="15"/>
+      <c r="O85" s="15"/>
+      <c r="P85" s="15"/>
+      <c r="Q85" s="15"/>
+      <c r="R85" s="15"/>
+      <c r="S85" s="15"/>
+      <c r="T85" s="15"/>
+      <c r="U85" s="15"/>
       <c r="V85" s="15"/>
     </row>
     <row r="86" ht="15.0" customHeight="1">
-      <c r="A86" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="B86" s="15"/>
-      <c r="C86" s="21">
-        <v>-1.03</v>
-      </c>
-      <c r="D86" s="21">
-        <v>-1.01</v>
-      </c>
-      <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="15"/>
-      <c r="M86" s="15"/>
-      <c r="N86" s="15"/>
-      <c r="O86" s="15"/>
-      <c r="P86" s="15"/>
-      <c r="Q86" s="15"/>
-      <c r="R86" s="15"/>
-      <c r="S86" s="15"/>
-      <c r="T86" s="15"/>
-      <c r="U86" s="15"/>
-      <c r="V86" s="15"/>
+      <c r="A86" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" s="22">
+        <v>13317.33</v>
+      </c>
+      <c r="C86" s="22">
+        <v>11986.57</v>
+      </c>
+      <c r="D86" s="22">
+        <v>11042.19</v>
+      </c>
+      <c r="E86" s="22">
+        <v>11391.19</v>
+      </c>
+      <c r="F86" s="22">
+        <v>11445.83</v>
+      </c>
+      <c r="G86" s="19">
+        <v>9492.83</v>
+      </c>
+      <c r="H86" s="19">
+        <v>7900.75</v>
+      </c>
+      <c r="I86" s="19">
+        <v>7601.95</v>
+      </c>
+      <c r="J86" s="19">
+        <v>6845.42</v>
+      </c>
+      <c r="K86" s="19">
+        <v>4049.32</v>
+      </c>
+      <c r="L86" s="19">
+        <v>3828.33</v>
+      </c>
+      <c r="M86" s="19">
+        <v>3225.36</v>
+      </c>
+      <c r="N86" s="19">
+        <v>3048.84</v>
+      </c>
+      <c r="O86" s="19">
+        <v>2641.77</v>
+      </c>
+      <c r="P86" s="19">
+        <v>2364.04</v>
+      </c>
+      <c r="Q86" s="19">
+        <v>1317.33</v>
+      </c>
+      <c r="R86" s="19">
+        <v>934.13</v>
+      </c>
+      <c r="S86" s="19">
+        <v>960.91</v>
+      </c>
+      <c r="T86" s="19">
+        <v>1151.55</v>
+      </c>
+      <c r="U86" s="19">
+        <v>1107.19</v>
+      </c>
+      <c r="V86" s="19">
+        <v>498.2</v>
+      </c>
     </row>
     <row r="87" ht="15.0" customHeight="1">
-      <c r="A87" s="18" t="s">
+      <c r="A87" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="E87" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="F87" s="17">
+        <v>72.1</v>
+      </c>
+      <c r="G87" s="17">
+        <v>59.52</v>
+      </c>
+      <c r="H87" s="17">
+        <v>54.38</v>
+      </c>
+      <c r="I87" s="17">
+        <v>47.82</v>
+      </c>
+      <c r="J87" s="17">
+        <v>45.03</v>
+      </c>
+      <c r="K87" s="17">
+        <v>40.78</v>
+      </c>
+      <c r="L87" s="17">
+        <v>37.68</v>
+      </c>
+      <c r="M87" s="15"/>
+      <c r="N87" s="15"/>
+      <c r="O87" s="15"/>
+      <c r="P87" s="15"/>
+      <c r="Q87" s="15"/>
+      <c r="R87" s="15"/>
+      <c r="S87" s="15"/>
+      <c r="T87" s="15"/>
+      <c r="U87" s="15"/>
+      <c r="V87" s="15"/>
+    </row>
+    <row r="88" ht="15.0" customHeight="1">
+      <c r="A88" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B88" s="22"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="E88" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="F88" s="20">
+        <v>72.1</v>
+      </c>
+      <c r="G88" s="20">
+        <v>59.52</v>
+      </c>
+      <c r="H88" s="20">
+        <v>54.38</v>
+      </c>
+      <c r="I88" s="20">
+        <v>47.82</v>
+      </c>
+      <c r="J88" s="20">
+        <v>45.03</v>
+      </c>
+      <c r="K88" s="20">
+        <v>40.78</v>
+      </c>
+      <c r="L88" s="20">
+        <v>37.68</v>
+      </c>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="T88" s="22"/>
+      <c r="U88" s="22"/>
+      <c r="V88" s="22"/>
+    </row>
+    <row r="89" ht="15.0" customHeight="1">
+      <c r="A89" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="17">
+        <v>0.97</v>
+      </c>
+      <c r="G89" s="15"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="K89" s="15"/>
+      <c r="L89" s="15"/>
+      <c r="M89" s="15"/>
+      <c r="N89" s="15"/>
+      <c r="O89" s="15"/>
+      <c r="P89" s="15"/>
+      <c r="Q89" s="15"/>
+      <c r="R89" s="15"/>
+      <c r="S89" s="15"/>
+      <c r="T89" s="15"/>
+      <c r="U89" s="15"/>
+      <c r="V89" s="15"/>
+    </row>
+    <row r="90" ht="15.0" customHeight="1">
+      <c r="A90" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B87" s="22">
+      <c r="B90" s="22">
         <v>13317.33</v>
       </c>
-      <c r="C87" s="22">
+      <c r="C90" s="22">
         <v>11986.57</v>
       </c>
-      <c r="D87" s="22">
+      <c r="D90" s="22">
         <v>11042.19</v>
       </c>
-      <c r="E87" s="22">
+      <c r="E90" s="22">
         <v>11391.19</v>
       </c>
-      <c r="F87" s="22">
-        <v>11445.83</v>
-      </c>
-      <c r="G87" s="19">
-        <v>9492.83</v>
-      </c>
-      <c r="H87" s="19">
-        <v>7900.75</v>
-      </c>
-      <c r="I87" s="19">
-        <v>7601.95</v>
-      </c>
-      <c r="J87" s="19">
-        <v>6845.42</v>
-      </c>
-      <c r="K87" s="19">
-        <v>4049.32</v>
-      </c>
-      <c r="L87" s="19">
-        <v>3828.33</v>
-      </c>
-      <c r="M87" s="19">
+      <c r="F90" s="22">
+        <v>11518.9</v>
+      </c>
+      <c r="G90" s="19">
+        <v>9552.35</v>
+      </c>
+      <c r="H90" s="19">
+        <v>7955.13</v>
+      </c>
+      <c r="I90" s="19">
+        <v>7649.76</v>
+      </c>
+      <c r="J90" s="19">
+        <v>6891.45</v>
+      </c>
+      <c r="K90" s="19">
+        <v>4090.1</v>
+      </c>
+      <c r="L90" s="19">
+        <v>3866.01</v>
+      </c>
+      <c r="M90" s="19">
         <v>3225.36</v>
       </c>
-      <c r="N87" s="19">
+      <c r="N90" s="19">
         <v>3048.84</v>
       </c>
-      <c r="O87" s="19">
+      <c r="O90" s="19">
         <v>2641.77</v>
       </c>
-      <c r="P87" s="19">
+      <c r="P90" s="19">
         <v>2364.04</v>
       </c>
-      <c r="Q87" s="19">
+      <c r="Q90" s="19">
         <v>1317.33</v>
       </c>
-      <c r="R87" s="19">
+      <c r="R90" s="19">
         <v>934.13</v>
       </c>
-      <c r="S87" s="19">
+      <c r="S90" s="19">
         <v>960.91</v>
       </c>
-      <c r="T87" s="19">
+      <c r="T90" s="19">
         <v>1151.55</v>
       </c>
-      <c r="U87" s="19">
+      <c r="U90" s="19">
         <v>1107.19</v>
       </c>
-      <c r="V87" s="19">
+      <c r="V90" s="19">
         <v>498.2</v>
       </c>
     </row>
-    <row r="88" ht="15.0" customHeight="1">
-      <c r="A88" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="E88" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F88" s="17">
-        <v>72.1</v>
-      </c>
-      <c r="G88" s="17">
-        <v>59.52</v>
-      </c>
-      <c r="H88" s="17">
-        <v>54.38</v>
-      </c>
-      <c r="I88" s="17">
-        <v>47.82</v>
-      </c>
-      <c r="J88" s="17">
-        <v>45.03</v>
-      </c>
-      <c r="K88" s="17">
-        <v>40.78</v>
-      </c>
-      <c r="L88" s="17">
-        <v>37.68</v>
-      </c>
-      <c r="M88" s="15"/>
-      <c r="N88" s="15"/>
-      <c r="O88" s="15"/>
-      <c r="P88" s="15"/>
-      <c r="Q88" s="15"/>
-      <c r="R88" s="15"/>
-      <c r="S88" s="15"/>
-      <c r="T88" s="15"/>
-      <c r="U88" s="15"/>
-      <c r="V88" s="15"/>
-    </row>
-    <row r="89" ht="15.0" customHeight="1">
-      <c r="A89" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="E89" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="F89" s="20">
-        <v>72.1</v>
-      </c>
-      <c r="G89" s="20">
-        <v>59.52</v>
-      </c>
-      <c r="H89" s="20">
-        <v>54.38</v>
-      </c>
-      <c r="I89" s="20">
-        <v>47.82</v>
-      </c>
-      <c r="J89" s="20">
-        <v>45.03</v>
-      </c>
-      <c r="K89" s="20">
-        <v>40.78</v>
-      </c>
-      <c r="L89" s="20">
-        <v>37.68</v>
-      </c>
-      <c r="M89" s="22"/>
-      <c r="N89" s="22"/>
-      <c r="O89" s="22"/>
-      <c r="P89" s="22"/>
-      <c r="Q89" s="22"/>
-      <c r="R89" s="22"/>
-      <c r="S89" s="22"/>
-      <c r="T89" s="22"/>
-      <c r="U89" s="22"/>
-      <c r="V89" s="22"/>
-    </row>
-    <row r="90" ht="15.0" customHeight="1">
-      <c r="A90" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B90" s="15"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="17">
-        <v>0.97</v>
-      </c>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="K90" s="15"/>
-      <c r="L90" s="15"/>
-      <c r="M90" s="15"/>
-      <c r="N90" s="15"/>
-      <c r="O90" s="15"/>
-      <c r="P90" s="15"/>
-      <c r="Q90" s="15"/>
-      <c r="R90" s="15"/>
-      <c r="S90" s="15"/>
-      <c r="T90" s="15"/>
-      <c r="U90" s="15"/>
-      <c r="V90" s="15"/>
-    </row>
     <row r="91" ht="15.0" customHeight="1">
-      <c r="A91" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B91" s="22">
-        <v>13317.33</v>
-      </c>
-      <c r="C91" s="22">
-        <v>11986.57</v>
-      </c>
-      <c r="D91" s="22">
-        <v>11042.19</v>
-      </c>
-      <c r="E91" s="22">
-        <v>11391.19</v>
-      </c>
-      <c r="F91" s="22">
-        <v>11518.9</v>
-      </c>
-      <c r="G91" s="19">
-        <v>9552.35</v>
-      </c>
-      <c r="H91" s="19">
-        <v>7955.13</v>
-      </c>
-      <c r="I91" s="19">
-        <v>7649.76</v>
-      </c>
-      <c r="J91" s="19">
-        <v>6891.45</v>
-      </c>
-      <c r="K91" s="19">
-        <v>4090.1</v>
-      </c>
-      <c r="L91" s="19">
-        <v>3866.01</v>
-      </c>
-      <c r="M91" s="19">
-        <v>3225.36</v>
-      </c>
-      <c r="N91" s="19">
-        <v>3048.84</v>
-      </c>
-      <c r="O91" s="19">
-        <v>2641.77</v>
-      </c>
-      <c r="P91" s="19">
-        <v>2364.04</v>
-      </c>
-      <c r="Q91" s="19">
-        <v>1317.33</v>
-      </c>
-      <c r="R91" s="19">
-        <v>934.13</v>
-      </c>
-      <c r="S91" s="19">
-        <v>960.91</v>
-      </c>
-      <c r="T91" s="19">
-        <v>1151.55</v>
-      </c>
-      <c r="U91" s="19">
-        <v>1107.19</v>
-      </c>
-      <c r="V91" s="19">
-        <v>498.2</v>
-      </c>
+      <c r="A91" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B91" s="21">
+        <v>-1.09</v>
+      </c>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="15"/>
+      <c r="M91" s="15"/>
+      <c r="N91" s="15"/>
+      <c r="O91" s="15"/>
+      <c r="P91" s="15"/>
+      <c r="Q91" s="15"/>
+      <c r="R91" s="15"/>
+      <c r="S91" s="15"/>
+      <c r="T91" s="15"/>
+      <c r="U91" s="15"/>
+      <c r="V91" s="15"/>
     </row>
     <row r="92" ht="15.0" customHeight="1">
-      <c r="A92" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="B92" s="21">
-        <v>-1.09</v>
-      </c>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
-      <c r="M92" s="15"/>
-      <c r="N92" s="15"/>
-      <c r="O92" s="15"/>
-      <c r="P92" s="15"/>
-      <c r="Q92" s="15"/>
-      <c r="R92" s="15"/>
-      <c r="S92" s="15"/>
-      <c r="T92" s="15"/>
-      <c r="U92" s="15"/>
-      <c r="V92" s="15"/>
+      <c r="A92" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B92" s="22">
+        <v>36482.42</v>
+      </c>
+      <c r="C92" s="22">
+        <v>33130.38</v>
+      </c>
+      <c r="D92" s="22">
+        <v>31928.53</v>
+      </c>
+      <c r="E92" s="22">
+        <v>29869.17</v>
+      </c>
+      <c r="F92" s="22">
+        <v>28679.84</v>
+      </c>
+      <c r="G92" s="22">
+        <v>25990.16</v>
+      </c>
+      <c r="H92" s="22">
+        <v>21741.59</v>
+      </c>
+      <c r="I92" s="22">
+        <v>20548.68</v>
+      </c>
+      <c r="J92" s="22">
+        <v>19720.74</v>
+      </c>
+      <c r="K92" s="22">
+        <v>13200.59</v>
+      </c>
+      <c r="L92" s="22">
+        <v>14133.84</v>
+      </c>
+      <c r="M92" s="22">
+        <v>11827.91</v>
+      </c>
+      <c r="N92" s="22">
+        <v>11361.29</v>
+      </c>
+      <c r="O92" s="22">
+        <v>10437.68</v>
+      </c>
+      <c r="P92" s="22">
+        <v>10307.44</v>
+      </c>
+      <c r="Q92" s="19">
+        <v>4658.18</v>
+      </c>
+      <c r="R92" s="19">
+        <v>3350.13</v>
+      </c>
+      <c r="S92" s="19">
+        <v>3656.24</v>
+      </c>
+      <c r="T92" s="19">
+        <v>3609.5</v>
+      </c>
+      <c r="U92" s="19">
+        <v>2249.02</v>
+      </c>
+      <c r="V92" s="19">
+        <v>1553.79</v>
+      </c>
     </row>
     <row r="93" ht="15.0" customHeight="1">
-      <c r="A93" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B93" s="22">
-        <v>36482.42</v>
-      </c>
-      <c r="C93" s="22">
-        <v>33130.38</v>
-      </c>
-      <c r="D93" s="22">
-        <v>31928.53</v>
-      </c>
-      <c r="E93" s="22">
-        <v>29869.17</v>
-      </c>
-      <c r="F93" s="22">
-        <v>28679.84</v>
-      </c>
-      <c r="G93" s="22">
-        <v>25990.16</v>
-      </c>
-      <c r="H93" s="22">
-        <v>21741.59</v>
-      </c>
-      <c r="I93" s="22">
-        <v>20548.68</v>
-      </c>
-      <c r="J93" s="22">
-        <v>19720.74</v>
-      </c>
-      <c r="K93" s="22">
-        <v>13200.59</v>
-      </c>
-      <c r="L93" s="22">
-        <v>14133.84</v>
-      </c>
-      <c r="M93" s="22">
-        <v>11827.91</v>
-      </c>
-      <c r="N93" s="22">
-        <v>11361.29</v>
-      </c>
-      <c r="O93" s="22">
-        <v>10437.68</v>
-      </c>
-      <c r="P93" s="22">
-        <v>10307.44</v>
-      </c>
-      <c r="Q93" s="19">
-        <v>4658.18</v>
-      </c>
-      <c r="R93" s="19">
-        <v>3350.13</v>
-      </c>
-      <c r="S93" s="19">
-        <v>3656.24</v>
-      </c>
-      <c r="T93" s="19">
-        <v>3609.5</v>
-      </c>
-      <c r="U93" s="19">
-        <v>2249.02</v>
-      </c>
-      <c r="V93" s="19">
-        <v>1553.79</v>
+      <c r="A93" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B93" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="C93" s="16">
+        <v>141.43</v>
+      </c>
+      <c r="D93" s="16">
+        <v>141.43</v>
+      </c>
+      <c r="E93" s="16">
+        <v>141.43</v>
+      </c>
+      <c r="F93" s="16">
+        <v>141.34</v>
+      </c>
+      <c r="G93" s="16">
+        <v>134.07</v>
+      </c>
+      <c r="H93" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="I93" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="J93" s="16">
+        <v>132.04</v>
+      </c>
+      <c r="K93" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="L93" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="M93" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="N93" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="O93" s="17">
+        <v>94.65</v>
+      </c>
+      <c r="P93" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="Q93" s="17">
+        <v>47.64</v>
+      </c>
+      <c r="R93" s="17">
+        <v>40.55</v>
+      </c>
+      <c r="S93" s="17">
+        <v>40.55</v>
+      </c>
+      <c r="T93" s="17">
+        <v>42.94</v>
+      </c>
+      <c r="U93" s="17">
+        <v>42.46</v>
+      </c>
+      <c r="V93" s="17">
+        <v>26.89</v>
       </c>
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B94" s="16">
         <v>141.79</v>
       </c>
       <c r="C94" s="16">
-        <v>141.43</v>
+        <v>141.79</v>
       </c>
       <c r="D94" s="16">
-        <v>141.43</v>
+        <v>141.79</v>
       </c>
       <c r="E94" s="16">
-        <v>141.43</v>
+        <v>141.79</v>
       </c>
       <c r="F94" s="16">
-        <v>141.34</v>
+        <v>141.79</v>
       </c>
       <c r="G94" s="16">
-        <v>134.07</v>
+        <v>134.51</v>
       </c>
       <c r="H94" s="16">
         <v>134.51</v>
@@ -12366,7 +12408,7 @@
         <v>95.29</v>
       </c>
       <c r="O94" s="17">
-        <v>94.65</v>
+        <v>95.29</v>
       </c>
       <c r="P94" s="17">
         <v>95.29</v>
@@ -12375,13 +12417,13 @@
         <v>47.64</v>
       </c>
       <c r="R94" s="17">
-        <v>40.55</v>
+        <v>43.31</v>
       </c>
       <c r="S94" s="17">
-        <v>40.55</v>
+        <v>43.31</v>
       </c>
       <c r="T94" s="17">
-        <v>42.94</v>
+        <v>43.31</v>
       </c>
       <c r="U94" s="17">
         <v>42.46</v>
@@ -12392,168 +12434,140 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B95" s="16">
-        <v>141.79</v>
-      </c>
-      <c r="C95" s="16">
-        <v>141.79</v>
-      </c>
-      <c r="D95" s="16">
-        <v>141.79</v>
-      </c>
-      <c r="E95" s="16">
-        <v>141.79</v>
-      </c>
-      <c r="F95" s="16">
-        <v>141.79</v>
-      </c>
-      <c r="G95" s="16">
-        <v>134.51</v>
-      </c>
-      <c r="H95" s="16">
-        <v>134.51</v>
-      </c>
-      <c r="I95" s="16">
-        <v>134.51</v>
-      </c>
-      <c r="J95" s="16">
-        <v>132.04</v>
-      </c>
-      <c r="K95" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="L95" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="M95" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="N95" s="17">
-        <v>95.29</v>
+        <v>233</v>
+      </c>
+      <c r="B95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C95" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="D95" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="E95" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="F95" s="17">
+        <v>0.44</v>
+      </c>
+      <c r="G95" s="17">
+        <v>0.44</v>
+      </c>
+      <c r="H95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="M95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="N95" s="15">
+        <v>0.0</v>
       </c>
       <c r="O95" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="P95" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="Q95" s="17">
-        <v>47.64</v>
+        <v>0.64</v>
+      </c>
+      <c r="P95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="Q95" s="15">
+        <v>0.0</v>
       </c>
       <c r="R95" s="17">
-        <v>43.31</v>
+        <v>2.76</v>
       </c>
       <c r="S95" s="17">
-        <v>43.31</v>
+        <v>2.76</v>
       </c>
       <c r="T95" s="17">
-        <v>43.31</v>
-      </c>
-      <c r="U95" s="17">
-        <v>42.46</v>
-      </c>
-      <c r="V95" s="17">
-        <v>26.89</v>
+        <v>0.38</v>
+      </c>
+      <c r="U95" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="V95" s="15">
+        <v>0.0</v>
       </c>
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C96" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="D96" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="E96" s="17">
-        <v>0.35</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
       <c r="F96" s="17">
-        <v>0.44</v>
+        <v>95.19</v>
       </c>
       <c r="G96" s="17">
-        <v>0.44</v>
-      </c>
-      <c r="H96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="M96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="N96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="O96" s="17">
-        <v>0.64</v>
-      </c>
-      <c r="P96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="Q96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="R96" s="17">
-        <v>2.76</v>
-      </c>
-      <c r="S96" s="17">
-        <v>2.76</v>
-      </c>
-      <c r="T96" s="17">
-        <v>0.38</v>
-      </c>
-      <c r="U96" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="V96" s="15">
-        <v>0.0</v>
-      </c>
+        <v>83.22</v>
+      </c>
+      <c r="H96" s="17">
+        <v>68.82</v>
+      </c>
+      <c r="I96" s="17">
+        <v>65.97</v>
+      </c>
+      <c r="J96" s="17">
+        <v>59.74</v>
+      </c>
+      <c r="K96" s="17">
+        <v>53.11</v>
+      </c>
+      <c r="L96" s="17">
+        <v>51.71</v>
+      </c>
+      <c r="M96" s="15"/>
+      <c r="N96" s="15"/>
+      <c r="O96" s="15"/>
+      <c r="P96" s="15"/>
+      <c r="Q96" s="15"/>
+      <c r="R96" s="15"/>
+      <c r="S96" s="15"/>
+      <c r="T96" s="15"/>
+      <c r="U96" s="15"/>
+      <c r="V96" s="15"/>
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
       <c r="D97" s="15"/>
       <c r="E97" s="15"/>
       <c r="F97" s="17">
-        <v>95.19</v>
+        <v>92.75</v>
       </c>
       <c r="G97" s="17">
-        <v>83.22</v>
+        <v>80.93</v>
       </c>
       <c r="H97" s="17">
-        <v>68.82</v>
+        <v>66.95</v>
       </c>
       <c r="I97" s="17">
-        <v>65.97</v>
+        <v>64.21</v>
       </c>
       <c r="J97" s="17">
-        <v>59.74</v>
+        <v>58.04</v>
       </c>
       <c r="K97" s="17">
-        <v>53.11</v>
+        <v>50.92</v>
       </c>
       <c r="L97" s="17">
-        <v>51.71</v>
+        <v>48.18</v>
       </c>
       <c r="M97" s="15"/>
       <c r="N97" s="15"/>
@@ -12568,236 +12582,260 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
       <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="17">
-        <v>92.75</v>
-      </c>
-      <c r="G98" s="17">
-        <v>80.93</v>
-      </c>
-      <c r="H98" s="17">
-        <v>66.95</v>
-      </c>
-      <c r="I98" s="17">
-        <v>64.21</v>
-      </c>
-      <c r="J98" s="17">
-        <v>58.04</v>
-      </c>
-      <c r="K98" s="17">
-        <v>50.92</v>
-      </c>
-      <c r="L98" s="17">
-        <v>48.18</v>
-      </c>
-      <c r="M98" s="15"/>
-      <c r="N98" s="15"/>
-      <c r="O98" s="15"/>
-      <c r="P98" s="15"/>
-      <c r="Q98" s="15"/>
-      <c r="R98" s="15"/>
-      <c r="S98" s="15"/>
-      <c r="T98" s="15"/>
-      <c r="U98" s="15"/>
+      <c r="E98" s="15">
+        <v>15314.38</v>
+      </c>
+      <c r="F98" s="15">
+        <v>14393.02</v>
+      </c>
+      <c r="G98" s="15">
+        <v>13834.62</v>
+      </c>
+      <c r="H98" s="15">
+        <v>11387.92</v>
+      </c>
+      <c r="I98" s="15">
+        <v>10831.07</v>
+      </c>
+      <c r="J98" s="15">
+        <v>11111.18</v>
+      </c>
+      <c r="K98" s="16">
+        <v>7597.93</v>
+      </c>
+      <c r="L98" s="16">
+        <v>8497.05</v>
+      </c>
+      <c r="M98" s="16">
+        <v>7352.67</v>
+      </c>
+      <c r="N98" s="16">
+        <v>7222.98</v>
+      </c>
+      <c r="O98" s="16">
+        <v>6756.3</v>
+      </c>
+      <c r="P98" s="16">
+        <v>6941.97</v>
+      </c>
+      <c r="Q98" s="16">
+        <v>3155.97</v>
+      </c>
+      <c r="R98" s="16">
+        <v>2248.61</v>
+      </c>
+      <c r="S98" s="16">
+        <v>2708.39</v>
+      </c>
+      <c r="T98" s="16">
+        <v>2276.18</v>
+      </c>
+      <c r="U98" s="16">
+        <v>1047.1</v>
+      </c>
       <c r="V98" s="15"/>
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" s="15"/>
-      <c r="E99" s="15">
-        <v>15314.38</v>
-      </c>
-      <c r="F99" s="15">
-        <v>14393.02</v>
-      </c>
-      <c r="G99" s="15">
-        <v>13834.62</v>
-      </c>
-      <c r="H99" s="15">
-        <v>11387.92</v>
-      </c>
-      <c r="I99" s="15">
-        <v>10831.07</v>
-      </c>
-      <c r="J99" s="15">
-        <v>11111.18</v>
-      </c>
-      <c r="K99" s="16">
-        <v>7597.93</v>
-      </c>
-      <c r="L99" s="16">
-        <v>8497.05</v>
-      </c>
-      <c r="M99" s="16">
-        <v>7352.67</v>
-      </c>
-      <c r="N99" s="16">
-        <v>7222.98</v>
-      </c>
-      <c r="O99" s="16">
-        <v>6756.3</v>
+      <c r="E99" s="15"/>
+      <c r="F99" s="15"/>
+      <c r="G99" s="15"/>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
+      <c r="L99" s="15"/>
+      <c r="M99" s="15"/>
+      <c r="N99" s="15"/>
+      <c r="O99" s="15">
+        <v>0.0</v>
       </c>
       <c r="P99" s="16">
-        <v>6941.97</v>
+        <v>3210.52</v>
       </c>
       <c r="Q99" s="16">
-        <v>3155.97</v>
-      </c>
-      <c r="R99" s="16">
-        <v>2248.61</v>
-      </c>
-      <c r="S99" s="16">
-        <v>2708.39</v>
-      </c>
-      <c r="T99" s="16">
-        <v>2276.18</v>
-      </c>
-      <c r="U99" s="16">
-        <v>1047.1</v>
+        <v>3020.61</v>
+      </c>
+      <c r="R99" s="15"/>
+      <c r="S99" s="15"/>
+      <c r="T99" s="15"/>
+      <c r="U99" s="15">
+        <v>0.0</v>
       </c>
       <c r="V99" s="15"/>
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
       <c r="D100" s="15"/>
       <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
+      <c r="F100" s="21">
+        <v>-0.97</v>
+      </c>
+      <c r="G100" s="21">
+        <v>-1.04</v>
+      </c>
+      <c r="H100" s="21">
+        <v>-0.94</v>
+      </c>
       <c r="I100" s="15"/>
-      <c r="J100" s="15"/>
-      <c r="K100" s="15"/>
-      <c r="L100" s="15"/>
+      <c r="J100" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="K100" s="21">
+        <v>-0.95</v>
+      </c>
+      <c r="L100" s="17">
+        <v>1.05</v>
+      </c>
       <c r="M100" s="15"/>
       <c r="N100" s="15"/>
-      <c r="O100" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="P100" s="16">
-        <v>3210.52</v>
-      </c>
-      <c r="Q100" s="16">
-        <v>3020.61</v>
-      </c>
+      <c r="O100" s="15"/>
+      <c r="P100" s="15"/>
+      <c r="Q100" s="15"/>
       <c r="R100" s="15"/>
       <c r="S100" s="15"/>
       <c r="T100" s="15"/>
-      <c r="U100" s="15">
-        <v>0.0</v>
-      </c>
+      <c r="U100" s="15"/>
       <c r="V100" s="15"/>
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="B101" s="15"/>
-      <c r="C101" s="15"/>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="21">
-        <v>-0.97</v>
-      </c>
-      <c r="G101" s="21">
-        <v>-1.04</v>
-      </c>
-      <c r="H101" s="21">
-        <v>-0.94</v>
-      </c>
-      <c r="I101" s="15"/>
-      <c r="J101" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="K101" s="21">
-        <v>-0.95</v>
-      </c>
-      <c r="L101" s="17">
-        <v>1.05</v>
-      </c>
-      <c r="M101" s="15"/>
-      <c r="N101" s="15"/>
-      <c r="O101" s="15"/>
-      <c r="P101" s="15"/>
-      <c r="Q101" s="15"/>
-      <c r="R101" s="15"/>
-      <c r="S101" s="15"/>
-      <c r="T101" s="15"/>
-      <c r="U101" s="15"/>
+        <v>239</v>
+      </c>
+      <c r="B101" s="16">
+        <v>3192.92</v>
+      </c>
+      <c r="C101" s="16">
+        <v>3251.87</v>
+      </c>
+      <c r="D101" s="16">
+        <v>6617.46</v>
+      </c>
+      <c r="E101" s="16">
+        <v>3767.88</v>
+      </c>
+      <c r="F101" s="16">
+        <v>3824.04</v>
+      </c>
+      <c r="G101" s="16">
+        <v>3159.75</v>
+      </c>
+      <c r="H101" s="16">
+        <v>5542.53</v>
+      </c>
+      <c r="I101" s="16">
+        <v>2359.63</v>
+      </c>
+      <c r="J101" s="16">
+        <v>2067.34</v>
+      </c>
+      <c r="K101" s="16">
+        <v>2187.77</v>
+      </c>
+      <c r="L101" s="16">
+        <v>1444.26</v>
+      </c>
+      <c r="M101" s="16">
+        <v>1746.39</v>
+      </c>
+      <c r="N101" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="O101" s="16">
+        <v>758.03</v>
+      </c>
+      <c r="P101" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="Q101" s="16">
+        <v>135.35</v>
+      </c>
+      <c r="R101" s="16">
+        <v>355.29</v>
+      </c>
+      <c r="S101" s="16">
+        <v>270.33</v>
+      </c>
+      <c r="T101" s="16">
+        <v>233.44</v>
+      </c>
+      <c r="U101" s="15">
+        <v>0.0</v>
+      </c>
       <c r="V101" s="15"/>
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B102" s="16">
-        <v>3192.92</v>
+        <v>6025.0</v>
       </c>
       <c r="C102" s="16">
-        <v>3251.87</v>
+        <v>4676.81</v>
       </c>
       <c r="D102" s="16">
-        <v>6617.46</v>
+        <v>1243.35</v>
       </c>
       <c r="E102" s="16">
-        <v>3767.88</v>
+        <v>6071.16</v>
       </c>
       <c r="F102" s="16">
-        <v>3824.04</v>
+        <v>5765.78</v>
       </c>
       <c r="G102" s="16">
-        <v>3159.75</v>
+        <v>4912.96</v>
       </c>
       <c r="H102" s="16">
-        <v>5542.53</v>
+        <v>2120.06</v>
       </c>
       <c r="I102" s="16">
-        <v>2359.63</v>
+        <v>5473.6</v>
       </c>
       <c r="J102" s="16">
-        <v>2067.34</v>
+        <v>2225.44</v>
       </c>
       <c r="K102" s="16">
-        <v>2187.77</v>
+        <v>2057.85</v>
       </c>
       <c r="L102" s="16">
-        <v>1444.26</v>
+        <v>2771.3</v>
       </c>
       <c r="M102" s="16">
-        <v>1746.39</v>
-      </c>
-      <c r="N102" s="15">
+        <v>2337.79</v>
+      </c>
+      <c r="N102" s="16">
+        <v>3099.73</v>
+      </c>
+      <c r="O102" s="15">
         <v>0.0</v>
       </c>
-      <c r="O102" s="16">
-        <v>758.03</v>
-      </c>
-      <c r="P102" s="15">
+      <c r="P102" s="16">
+        <v>774.62</v>
+      </c>
+      <c r="Q102" s="15"/>
+      <c r="R102" s="15">
         <v>0.0</v>
       </c>
-      <c r="Q102" s="16">
-        <v>135.35</v>
-      </c>
-      <c r="R102" s="16">
-        <v>355.29</v>
-      </c>
       <c r="S102" s="16">
-        <v>270.33</v>
-      </c>
-      <c r="T102" s="16">
-        <v>233.44</v>
+        <v>2438.06</v>
+      </c>
+      <c r="T102" s="15">
+        <v>0.0</v>
       </c>
       <c r="U102" s="15">
         <v>0.0</v>
@@ -12806,62 +12844,62 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B103" s="16">
-        <v>6025.0</v>
+        <v>4786.1</v>
       </c>
       <c r="C103" s="16">
-        <v>4676.81</v>
+        <v>4901.96</v>
       </c>
       <c r="D103" s="16">
-        <v>1243.35</v>
+        <v>3708.92</v>
       </c>
       <c r="E103" s="16">
-        <v>6071.16</v>
+        <v>748.31</v>
       </c>
       <c r="F103" s="16">
-        <v>5765.78</v>
+        <v>2894.58</v>
       </c>
       <c r="G103" s="16">
-        <v>4912.96</v>
+        <v>2994.77</v>
       </c>
       <c r="H103" s="16">
-        <v>2120.06</v>
+        <v>2030.04</v>
       </c>
       <c r="I103" s="16">
-        <v>5473.6</v>
+        <v>214.69</v>
       </c>
       <c r="J103" s="16">
-        <v>2225.44</v>
+        <v>5295.42</v>
       </c>
       <c r="K103" s="16">
-        <v>2057.85</v>
+        <v>2192.51</v>
       </c>
       <c r="L103" s="16">
-        <v>2771.3</v>
+        <v>1679.73</v>
       </c>
       <c r="M103" s="16">
-        <v>2337.79</v>
+        <v>1620.83</v>
       </c>
       <c r="N103" s="16">
-        <v>3099.73</v>
-      </c>
-      <c r="O103" s="15">
+        <v>827.48</v>
+      </c>
+      <c r="O103" s="16">
+        <v>2832.37</v>
+      </c>
+      <c r="P103" s="15">
         <v>0.0</v>
       </c>
-      <c r="P103" s="16">
-        <v>774.62</v>
-      </c>
       <c r="Q103" s="15"/>
-      <c r="R103" s="15">
+      <c r="R103" s="16">
+        <v>1893.32</v>
+      </c>
+      <c r="S103" s="15">
         <v>0.0</v>
       </c>
-      <c r="S103" s="16">
-        <v>2438.06</v>
-      </c>
-      <c r="T103" s="15">
-        <v>0.0</v>
+      <c r="T103" s="16">
+        <v>2042.74</v>
       </c>
       <c r="U103" s="15">
         <v>0.0</v>
@@ -12870,165 +12908,141 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B104" s="16">
-        <v>4786.1</v>
+        <v>562.04</v>
       </c>
       <c r="C104" s="16">
-        <v>4901.96</v>
+        <v>3336.17</v>
       </c>
       <c r="D104" s="16">
-        <v>3708.92</v>
+        <v>2430.33</v>
       </c>
       <c r="E104" s="16">
-        <v>748.31</v>
-      </c>
-      <c r="F104" s="16">
-        <v>2894.58</v>
+        <v>1739.46</v>
+      </c>
+      <c r="F104" s="15">
+        <v>0.0</v>
       </c>
       <c r="G104" s="16">
-        <v>2994.77</v>
+        <v>926.21</v>
       </c>
       <c r="H104" s="16">
-        <v>2030.04</v>
+        <v>1042.68</v>
       </c>
       <c r="I104" s="16">
-        <v>214.69</v>
-      </c>
-      <c r="J104" s="16">
-        <v>5295.42</v>
+        <v>2102.98</v>
+      </c>
+      <c r="J104" s="15">
+        <v>0.0</v>
       </c>
       <c r="K104" s="16">
-        <v>2192.51</v>
+        <v>544.33</v>
       </c>
       <c r="L104" s="16">
-        <v>1679.73</v>
+        <v>1546.82</v>
       </c>
       <c r="M104" s="16">
-        <v>1620.83</v>
+        <v>1647.66</v>
       </c>
       <c r="N104" s="16">
-        <v>827.48</v>
+        <v>3295.77</v>
       </c>
       <c r="O104" s="16">
-        <v>2832.37</v>
-      </c>
-      <c r="P104" s="15">
+        <v>3165.9</v>
+      </c>
+      <c r="P104" s="16">
+        <v>2956.83</v>
+      </c>
+      <c r="Q104" s="15"/>
+      <c r="R104" s="15"/>
+      <c r="S104" s="15"/>
+      <c r="T104" s="15">
         <v>0.0</v>
       </c>
-      <c r="Q104" s="15"/>
-      <c r="R104" s="16">
-        <v>1893.32</v>
-      </c>
-      <c r="S104" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="T104" s="16">
-        <v>2042.74</v>
-      </c>
-      <c r="U104" s="15">
-        <v>0.0</v>
+      <c r="U104" s="16">
+        <v>1047.1</v>
       </c>
       <c r="V104" s="15"/>
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B105" s="16">
-        <v>562.04</v>
+        <v>4456.97</v>
       </c>
       <c r="C105" s="16">
-        <v>3336.17</v>
+        <v>1326.24</v>
       </c>
       <c r="D105" s="16">
-        <v>2430.33</v>
+        <v>3217.62</v>
       </c>
       <c r="E105" s="16">
-        <v>1739.46</v>
-      </c>
-      <c r="F105" s="15">
-        <v>0.0</v>
+        <v>2987.58</v>
+      </c>
+      <c r="F105" s="16">
+        <v>1909.59</v>
       </c>
       <c r="G105" s="16">
-        <v>926.21</v>
+        <v>1841.97</v>
       </c>
       <c r="H105" s="16">
-        <v>1042.68</v>
+        <v>653.55</v>
       </c>
       <c r="I105" s="16">
-        <v>2102.98</v>
-      </c>
-      <c r="J105" s="15">
-        <v>0.0</v>
+        <v>680.17</v>
+      </c>
+      <c r="J105" s="16">
+        <v>1521.98</v>
       </c>
       <c r="K105" s="16">
-        <v>544.33</v>
+        <v>616.41</v>
       </c>
       <c r="L105" s="16">
-        <v>1546.82</v>
-      </c>
-      <c r="M105" s="16">
-        <v>1647.66</v>
-      </c>
-      <c r="N105" s="16">
-        <v>3295.77</v>
-      </c>
-      <c r="O105" s="16">
-        <v>3165.9</v>
-      </c>
-      <c r="P105" s="16">
-        <v>2956.83</v>
-      </c>
+        <v>1053.89</v>
+      </c>
+      <c r="M105" s="15"/>
+      <c r="N105" s="15"/>
+      <c r="O105" s="15"/>
+      <c r="P105" s="15"/>
       <c r="Q105" s="15"/>
       <c r="R105" s="15"/>
       <c r="S105" s="15"/>
-      <c r="T105" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="U105" s="16">
-        <v>1047.1</v>
-      </c>
+      <c r="T105" s="15"/>
+      <c r="U105" s="15"/>
       <c r="V105" s="15"/>
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="B106" s="16">
-        <v>4456.97</v>
-      </c>
-      <c r="C106" s="16">
-        <v>1326.24</v>
-      </c>
-      <c r="D106" s="16">
-        <v>3217.62</v>
-      </c>
-      <c r="E106" s="16">
-        <v>2987.58</v>
-      </c>
-      <c r="F106" s="16">
-        <v>1909.59</v>
-      </c>
-      <c r="G106" s="16">
-        <v>1841.97</v>
-      </c>
-      <c r="H106" s="16">
-        <v>653.55</v>
-      </c>
-      <c r="I106" s="16">
-        <v>680.17</v>
-      </c>
-      <c r="J106" s="16">
-        <v>1521.98</v>
-      </c>
-      <c r="K106" s="16">
-        <v>616.41</v>
-      </c>
-      <c r="L106" s="16">
-        <v>1053.89</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="B106" s="17">
+        <v>9.84</v>
+      </c>
+      <c r="C106" s="17">
+        <v>8.22</v>
+      </c>
+      <c r="D106" s="17">
+        <v>11.07</v>
+      </c>
+      <c r="E106" s="17">
+        <v>3.77</v>
+      </c>
+      <c r="F106" s="17">
+        <v>3.9</v>
+      </c>
+      <c r="G106" s="17">
+        <v>4.18</v>
+      </c>
+      <c r="H106" s="17">
+        <v>3.75</v>
+      </c>
+      <c r="I106" s="15"/>
+      <c r="J106" s="15"/>
+      <c r="K106" s="15"/>
+      <c r="L106" s="15"/>
       <c r="M106" s="15"/>
       <c r="N106" s="15"/>
       <c r="O106" s="15"/>
@@ -13042,28 +13056,28 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B107" s="17">
-        <v>9.84</v>
+        <v>40.46</v>
       </c>
       <c r="C107" s="17">
-        <v>8.22</v>
+        <v>34.96</v>
       </c>
       <c r="D107" s="17">
-        <v>11.07</v>
+        <v>43.29</v>
       </c>
       <c r="E107" s="17">
-        <v>3.77</v>
+        <v>15.06</v>
       </c>
       <c r="F107" s="17">
-        <v>3.9</v>
+        <v>15.59</v>
       </c>
       <c r="G107" s="17">
-        <v>4.18</v>
+        <v>16.71</v>
       </c>
       <c r="H107" s="17">
-        <v>3.75</v>
+        <v>15.0</v>
       </c>
       <c r="I107" s="15"/>
       <c r="J107" s="15"/>
@@ -13082,28 +13096,28 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B108" s="17">
-        <v>40.46</v>
+        <v>50.3</v>
       </c>
       <c r="C108" s="17">
-        <v>34.96</v>
+        <v>31.87</v>
       </c>
       <c r="D108" s="17">
-        <v>43.29</v>
+        <v>29.2</v>
       </c>
       <c r="E108" s="17">
-        <v>15.06</v>
+        <v>36.71</v>
       </c>
       <c r="F108" s="17">
-        <v>15.59</v>
+        <v>37.02</v>
       </c>
       <c r="G108" s="17">
-        <v>16.71</v>
+        <v>41.77</v>
       </c>
       <c r="H108" s="17">
-        <v>15.0</v>
+        <v>30.94</v>
       </c>
       <c r="I108" s="15"/>
       <c r="J108" s="15"/>
@@ -13122,28 +13136,22 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="B109" s="17">
-        <v>50.3</v>
-      </c>
-      <c r="C109" s="17">
-        <v>31.87</v>
-      </c>
-      <c r="D109" s="17">
-        <v>29.2</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="15"/>
       <c r="E109" s="17">
-        <v>36.71</v>
+        <v>55.53</v>
       </c>
       <c r="F109" s="17">
-        <v>37.02</v>
+        <v>56.51</v>
       </c>
       <c r="G109" s="17">
-        <v>41.77</v>
+        <v>62.65</v>
       </c>
       <c r="H109" s="17">
-        <v>30.94</v>
+        <v>49.7</v>
       </c>
       <c r="I109" s="15"/>
       <c r="J109" s="15"/>
@@ -13162,438 +13170,405 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="B110" s="15"/>
-      <c r="C110" s="15"/>
-      <c r="D110" s="15"/>
+        <v>248</v>
+      </c>
+      <c r="B110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="C110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="D110" s="17">
+        <v>1.0</v>
+      </c>
       <c r="E110" s="17">
-        <v>55.53</v>
+        <v>1.0</v>
       </c>
       <c r="F110" s="17">
-        <v>56.51</v>
+        <v>1.0</v>
       </c>
       <c r="G110" s="17">
-        <v>62.65</v>
+        <v>1.0</v>
       </c>
       <c r="H110" s="17">
-        <v>49.7</v>
-      </c>
-      <c r="I110" s="15"/>
-      <c r="J110" s="15"/>
-      <c r="K110" s="15"/>
-      <c r="L110" s="15"/>
-      <c r="M110" s="15"/>
-      <c r="N110" s="15"/>
-      <c r="O110" s="15"/>
-      <c r="P110" s="15"/>
-      <c r="Q110" s="15"/>
-      <c r="R110" s="15"/>
-      <c r="S110" s="15"/>
-      <c r="T110" s="15"/>
-      <c r="U110" s="15"/>
-      <c r="V110" s="15"/>
+        <v>1.0</v>
+      </c>
+      <c r="I110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="J110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="K110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="L110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="M110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="N110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="O110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="P110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="Q110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="R110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="S110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="T110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="U110" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="V110" s="17">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="B111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="C111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="E111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="F111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="G111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="H111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="I111" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="J111" s="17">
-        <v>1.0</v>
+        <v>249</v>
+      </c>
+      <c r="B111" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="C111" s="16">
+        <v>141.43</v>
+      </c>
+      <c r="D111" s="16">
+        <v>141.43</v>
+      </c>
+      <c r="E111" s="16">
+        <v>141.43</v>
+      </c>
+      <c r="F111" s="16">
+        <v>141.34</v>
+      </c>
+      <c r="G111" s="16">
+        <v>134.07</v>
+      </c>
+      <c r="H111" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="I111" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="J111" s="16">
+        <v>132.04</v>
       </c>
       <c r="K111" s="17">
-        <v>1.0</v>
+        <v>95.29</v>
       </c>
       <c r="L111" s="17">
-        <v>1.0</v>
+        <v>95.29</v>
       </c>
       <c r="M111" s="17">
-        <v>1.0</v>
+        <v>95.29</v>
       </c>
       <c r="N111" s="17">
-        <v>1.0</v>
+        <v>95.29</v>
       </c>
       <c r="O111" s="17">
-        <v>1.0</v>
+        <v>94.65</v>
       </c>
       <c r="P111" s="17">
-        <v>1.0</v>
+        <v>95.29</v>
       </c>
       <c r="Q111" s="17">
-        <v>1.0</v>
+        <v>47.64</v>
       </c>
       <c r="R111" s="17">
-        <v>1.0</v>
+        <v>40.55</v>
       </c>
       <c r="S111" s="17">
-        <v>1.0</v>
+        <v>40.55</v>
       </c>
       <c r="T111" s="17">
-        <v>1.0</v>
+        <v>42.94</v>
       </c>
       <c r="U111" s="17">
-        <v>1.0</v>
+        <v>42.46</v>
       </c>
       <c r="V111" s="17">
-        <v>1.0</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="B112" s="16">
-        <v>141.79</v>
-      </c>
-      <c r="C112" s="16">
-        <v>141.43</v>
-      </c>
-      <c r="D112" s="16">
-        <v>141.43</v>
-      </c>
-      <c r="E112" s="16">
-        <v>141.43</v>
-      </c>
-      <c r="F112" s="16">
-        <v>141.34</v>
-      </c>
-      <c r="G112" s="16">
-        <v>134.07</v>
-      </c>
-      <c r="H112" s="16">
-        <v>134.51</v>
-      </c>
-      <c r="I112" s="16">
-        <v>134.51</v>
-      </c>
-      <c r="J112" s="16">
-        <v>132.04</v>
-      </c>
-      <c r="K112" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="L112" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="M112" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="N112" s="17">
-        <v>95.29</v>
+        <v>250</v>
+      </c>
+      <c r="B112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C112" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="D112" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="E112" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="F112" s="17">
+        <v>0.44</v>
+      </c>
+      <c r="G112" s="17">
+        <v>0.44</v>
+      </c>
+      <c r="H112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="M112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="N112" s="15">
+        <v>0.0</v>
       </c>
       <c r="O112" s="17">
-        <v>94.65</v>
-      </c>
-      <c r="P112" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="Q112" s="17">
-        <v>47.64</v>
+        <v>0.64</v>
+      </c>
+      <c r="P112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="Q112" s="15">
+        <v>0.0</v>
       </c>
       <c r="R112" s="17">
-        <v>40.55</v>
+        <v>2.76</v>
       </c>
       <c r="S112" s="17">
-        <v>40.55</v>
+        <v>2.76</v>
       </c>
       <c r="T112" s="17">
-        <v>42.94</v>
-      </c>
-      <c r="U112" s="17">
-        <v>42.46</v>
-      </c>
-      <c r="V112" s="17">
-        <v>26.89</v>
+        <v>0.38</v>
+      </c>
+      <c r="U112" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="V112" s="15">
+        <v>0.0</v>
       </c>
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C113" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="D113" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="E113" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="F113" s="17">
-        <v>0.44</v>
-      </c>
-      <c r="G113" s="17">
-        <v>0.44</v>
-      </c>
-      <c r="H113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="M113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="N113" s="15">
-        <v>0.0</v>
+        <v>251</v>
+      </c>
+      <c r="B113" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="C113" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="D113" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="E113" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="F113" s="16">
+        <v>141.79</v>
+      </c>
+      <c r="G113" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="H113" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="I113" s="16">
+        <v>134.51</v>
+      </c>
+      <c r="J113" s="16">
+        <v>132.04</v>
+      </c>
+      <c r="K113" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="L113" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="M113" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="N113" s="17">
+        <v>95.29</v>
       </c>
       <c r="O113" s="17">
-        <v>0.64</v>
-      </c>
-      <c r="P113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="Q113" s="15">
-        <v>0.0</v>
+        <v>95.29</v>
+      </c>
+      <c r="P113" s="17">
+        <v>95.29</v>
+      </c>
+      <c r="Q113" s="17">
+        <v>47.64</v>
       </c>
       <c r="R113" s="17">
-        <v>2.76</v>
+        <v>43.31</v>
       </c>
       <c r="S113" s="17">
-        <v>2.76</v>
+        <v>43.31</v>
       </c>
       <c r="T113" s="17">
-        <v>0.38</v>
-      </c>
-      <c r="U113" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="V113" s="15">
-        <v>0.0</v>
+        <v>43.31</v>
+      </c>
+      <c r="U113" s="17">
+        <v>42.46</v>
+      </c>
+      <c r="V113" s="17">
+        <v>26.89</v>
       </c>
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B114" s="16">
-        <v>141.79</v>
+        <v>145.0</v>
       </c>
       <c r="C114" s="16">
-        <v>141.79</v>
+        <v>150.0</v>
       </c>
       <c r="D114" s="16">
-        <v>141.79</v>
+        <v>149.0</v>
       </c>
       <c r="E114" s="16">
-        <v>141.79</v>
+        <v>157.0</v>
       </c>
       <c r="F114" s="16">
-        <v>141.79</v>
+        <v>144.0</v>
       </c>
       <c r="G114" s="16">
-        <v>134.51</v>
+        <v>162.0</v>
       </c>
       <c r="H114" s="16">
-        <v>134.51</v>
+        <v>153.0</v>
       </c>
       <c r="I114" s="16">
-        <v>134.51</v>
+        <v>158.0</v>
       </c>
       <c r="J114" s="16">
-        <v>132.04</v>
-      </c>
-      <c r="K114" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="L114" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="M114" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="N114" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="O114" s="17">
-        <v>95.29</v>
-      </c>
-      <c r="P114" s="17">
-        <v>95.29</v>
+        <v>156.0</v>
+      </c>
+      <c r="K114" s="16">
+        <v>148.0</v>
+      </c>
+      <c r="L114" s="16">
+        <v>150.0</v>
+      </c>
+      <c r="M114" s="16">
+        <v>149.0</v>
+      </c>
+      <c r="N114" s="16">
+        <v>140.0</v>
+      </c>
+      <c r="O114" s="16">
+        <v>132.0</v>
+      </c>
+      <c r="P114" s="16">
+        <v>154.0</v>
       </c>
       <c r="Q114" s="17">
-        <v>47.64</v>
+        <v>64.0</v>
       </c>
       <c r="R114" s="17">
-        <v>43.31</v>
-      </c>
-      <c r="S114" s="17">
-        <v>43.31</v>
-      </c>
+        <v>55.0</v>
+      </c>
+      <c r="S114" s="15"/>
       <c r="T114" s="17">
-        <v>43.31</v>
+        <v>44.0</v>
       </c>
       <c r="U114" s="17">
-        <v>42.46</v>
-      </c>
-      <c r="V114" s="17">
-        <v>26.89</v>
-      </c>
+        <v>29.0</v>
+      </c>
+      <c r="V114" s="15"/>
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="B115" s="16">
-        <v>145.0</v>
-      </c>
-      <c r="C115" s="16">
-        <v>150.0</v>
-      </c>
-      <c r="D115" s="16">
-        <v>149.0</v>
-      </c>
-      <c r="E115" s="16">
-        <v>157.0</v>
-      </c>
-      <c r="F115" s="16">
-        <v>144.0</v>
-      </c>
-      <c r="G115" s="16">
-        <v>162.0</v>
-      </c>
-      <c r="H115" s="16">
-        <v>153.0</v>
-      </c>
-      <c r="I115" s="16">
-        <v>158.0</v>
-      </c>
-      <c r="J115" s="16">
-        <v>156.0</v>
-      </c>
-      <c r="K115" s="16">
-        <v>148.0</v>
-      </c>
-      <c r="L115" s="16">
-        <v>150.0</v>
+        <v>253</v>
+      </c>
+      <c r="B115" s="15">
+        <v>16500.0</v>
+      </c>
+      <c r="C115" s="15">
+        <v>15809.0</v>
+      </c>
+      <c r="D115" s="15">
+        <v>17636.0</v>
+      </c>
+      <c r="E115" s="15">
+        <v>19057.0</v>
+      </c>
+      <c r="F115" s="15">
+        <v>18733.0</v>
+      </c>
+      <c r="G115" s="15">
+        <v>18065.0</v>
+      </c>
+      <c r="H115" s="15">
+        <v>14688.0</v>
+      </c>
+      <c r="I115" s="15">
+        <v>13921.0</v>
+      </c>
+      <c r="J115" s="15">
+        <v>14513.0</v>
+      </c>
+      <c r="K115" s="15">
+        <v>11233.0</v>
+      </c>
+      <c r="L115" s="15">
+        <v>10329.0</v>
       </c>
       <c r="M115" s="16">
-        <v>149.0</v>
+        <v>6759.0</v>
       </c>
       <c r="N115" s="16">
-        <v>140.0</v>
+        <v>5524.0</v>
       </c>
       <c r="O115" s="16">
-        <v>132.0</v>
+        <v>2669.0</v>
       </c>
       <c r="P115" s="16">
-        <v>154.0</v>
-      </c>
-      <c r="Q115" s="17">
-        <v>64.0</v>
-      </c>
-      <c r="R115" s="17">
-        <v>55.0</v>
+        <v>2584.0</v>
+      </c>
+      <c r="Q115" s="16">
+        <v>2273.0</v>
+      </c>
+      <c r="R115" s="16">
+        <v>1789.0</v>
       </c>
       <c r="S115" s="15"/>
-      <c r="T115" s="17">
-        <v>44.0</v>
-      </c>
-      <c r="U115" s="17">
-        <v>29.0</v>
+      <c r="T115" s="16">
+        <v>1819.0</v>
+      </c>
+      <c r="U115" s="16">
+        <v>2294.0</v>
       </c>
       <c r="V115" s="15"/>
     </row>
-    <row r="116" ht="15.0" customHeight="1">
-      <c r="A116" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="B116" s="15">
-        <v>16500.0</v>
-      </c>
-      <c r="C116" s="15">
-        <v>15809.0</v>
-      </c>
-      <c r="D116" s="15">
-        <v>17636.0</v>
-      </c>
-      <c r="E116" s="15">
-        <v>19057.0</v>
-      </c>
-      <c r="F116" s="15">
-        <v>18733.0</v>
-      </c>
-      <c r="G116" s="15">
-        <v>18065.0</v>
-      </c>
-      <c r="H116" s="15">
-        <v>14688.0</v>
-      </c>
-      <c r="I116" s="15">
-        <v>13921.0</v>
-      </c>
-      <c r="J116" s="15">
-        <v>14513.0</v>
-      </c>
-      <c r="K116" s="15">
-        <v>11233.0</v>
-      </c>
-      <c r="L116" s="15">
-        <v>10329.0</v>
-      </c>
-      <c r="M116" s="16">
-        <v>6759.0</v>
-      </c>
-      <c r="N116" s="16">
-        <v>5524.0</v>
-      </c>
-      <c r="O116" s="16">
-        <v>2669.0</v>
-      </c>
-      <c r="P116" s="16">
-        <v>2584.0</v>
-      </c>
-      <c r="Q116" s="16">
-        <v>2273.0</v>
-      </c>
-      <c r="R116" s="16">
-        <v>1789.0</v>
-      </c>
-      <c r="S116" s="15"/>
-      <c r="T116" s="16">
-        <v>1819.0</v>
-      </c>
-      <c r="U116" s="16">
-        <v>2294.0</v>
-      </c>
-      <c r="V116" s="15"/>
-    </row>
+    <row r="116" ht="15.75" customHeight="1"/>
     <row r="117" ht="15.75" customHeight="1"/>
     <row r="118" ht="15.75" customHeight="1"/>
     <row r="119" ht="15.75" customHeight="1"/>
@@ -14477,7 +14452,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.5" right="0.5" top="1.0"/>
